--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -532,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-FEB-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6243</v>
+        <v>9369</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6474</v>
+        <v>10449</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-231</v>
+        <v>-1080</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>04-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +578,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-117</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6243</v>
+        <v>10049</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6474</v>
+        <v>10449</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-231</v>
+        <v>-400</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>04-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,26 +623,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7196</v>
+        <v>11014</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6474</v>
+        <v>11855</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>722</v>
+        <v>-841</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -667,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +668,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6243</v>
+        <v>11055</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6474</v>
+        <v>11855</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-231</v>
+        <v>-800</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12201</v>
+        <v>14805</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12632</v>
+        <v>16831</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-431</v>
+        <v>-2026</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -757,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,17 +758,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12353</v>
+        <v>8395</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12632</v>
+        <v>8464</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-279</v>
+        <v>-69</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +803,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13747</v>
+        <v>7044</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12632</v>
+        <v>9180</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1115</v>
+        <v>-2136</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +848,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12201</v>
+        <v>7609</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14228</v>
+        <v>9180</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2027</v>
+        <v>-1571</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -892,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,26 +893,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12353</v>
+        <v>10862</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14228</v>
+        <v>9180</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1875</v>
+        <v>1682</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -937,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +938,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>15191</v>
+        <v>7044</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14228</v>
+        <v>8601</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>963</v>
+        <v>-1557</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +973,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +983,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9806</v>
+        <v>7609</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11302</v>
+        <v>8601</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1496</v>
+        <v>-992</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1027,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1028,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10440</v>
+        <v>8105</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11302</v>
+        <v>8601</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-862</v>
+        <v>-496</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1072,7 +1063,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>07-APR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,33 +1073,843 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>6079</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-220</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>09-APR-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>6079</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-220</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>14-APR-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>6079</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-220</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>6079</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-220</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>17-APR-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>6079</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-220</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>17-APR-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>17-APR-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>18-APR-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>6809</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-675</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>18-APR-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-811</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>11111</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>11302</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-191</v>
-      </c>
-      <c r="G14" s="2" t="n">
+      <c r="D23" s="2" t="n">
+        <v>8753</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>6809</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>21-APR-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>23-APR-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>24-APR-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>6079</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-220</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>24-APR-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>24-APR-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>25-APR-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>6809</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-675</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>25-APR-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>8753</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>6809</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>28-APR-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>30-APR-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>6134</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>6299</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9369</v>
+        <v>7168</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10449</v>
+        <v>8838</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1080</v>
+        <v>-1670</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10049</v>
+        <v>7168</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10449</v>
+        <v>8838</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-400</v>
+        <v>-1670</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11014</v>
+        <v>7716</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11855</v>
+        <v>8838</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-841</v>
+        <v>-1122</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11055</v>
+        <v>7716</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11855</v>
+        <v>8838</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-800</v>
+        <v>-1122</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14805</v>
+        <v>8249</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16831</v>
+        <v>8403</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2026</v>
+        <v>-154</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -748,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8395</v>
+        <v>8249</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8464</v>
+        <v>8403</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-69</v>
+        <v>-154</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7044</v>
+        <v>8664</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9180</v>
+        <v>9567</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2136</v>
+        <v>-903</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7609</v>
+        <v>8664</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9180</v>
+        <v>9567</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1571</v>
+        <v>-903</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>07-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10862</v>
+        <v>7168</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9180</v>
+        <v>7182</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1682</v>
+        <v>-14</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -928,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>07-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7044</v>
+        <v>7168</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8601</v>
+        <v>7182</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1557</v>
+        <v>-14</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7609</v>
+        <v>7716</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8601</v>
+        <v>8403</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-992</v>
+        <v>-687</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1028,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8105</v>
+        <v>7716</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8601</v>
+        <v>8403</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-496</v>
+        <v>-687</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1073,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6079</v>
+        <v>8894</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6299</v>
+        <v>8403</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-220</v>
+        <v>491</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1118,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6079</v>
+        <v>8894</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6299</v>
+        <v>8403</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-220</v>
+        <v>491</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1153,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14-APR-26</t>
+          <t>10-APR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1163,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6079</v>
+        <v>6513</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6299</v>
+        <v>7182</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-220</v>
+        <v>-669</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1198,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>10-APR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1208,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6079</v>
+        <v>6513</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6299</v>
+        <v>7182</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-220</v>
+        <v>-669</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1243,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>11-APR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1257,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6134</v>
+        <v>8249</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6299</v>
+        <v>8992</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-165</v>
+        <v>-743</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1288,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>11-APR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1298,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6079</v>
+        <v>8249</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6299</v>
+        <v>8992</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-220</v>
+        <v>-743</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1333,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>11-APR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1343,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6134</v>
+        <v>11012</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>6299</v>
+        <v>8992</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-165</v>
+        <v>2020</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1378,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>11-APR-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1388,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6134</v>
+        <v>11012</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6299</v>
+        <v>8992</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-165</v>
+        <v>2020</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1423,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>16-APR-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1433,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6134</v>
+        <v>6172</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6809</v>
+        <v>6397</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-675</v>
+        <v>-225</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1468,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>16-APR-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1478,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8753</v>
+        <v>6172</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6809</v>
+        <v>6397</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1944</v>
+        <v>-225</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1513,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>21-APR-26</t>
+          <t>12-MAY-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1523,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6134</v>
+        <v>6397</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6299</v>
+        <v>10157</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-165</v>
+        <v>-3760</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1558,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>23-APR-26</t>
+          <t>12-MAY-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1568,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6134</v>
+        <v>6397</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>6299</v>
+        <v>10157</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-165</v>
+        <v>-3760</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1603,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>24-APR-26</t>
+          <t>12-MAY-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1613,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6079</v>
+        <v>8249</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>6299</v>
+        <v>10157</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-220</v>
+        <v>-1908</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1648,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>24-APR-26</t>
+          <t>12-MAY-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1658,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6134</v>
+        <v>8249</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>6299</v>
+        <v>10157</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-165</v>
+        <v>-1908</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1693,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>24-APR-26</t>
+          <t>12-MAY-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1703,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6134</v>
+        <v>10297</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6299</v>
+        <v>10157</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-165</v>
+        <v>140</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1738,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25-APR-26</t>
+          <t>12-MAY-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1748,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6134</v>
+        <v>10297</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>6809</v>
+        <v>10157</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-675</v>
+        <v>140</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1783,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>25-APR-26</t>
+          <t>14-MAY-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1793,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8753</v>
+        <v>6397</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>6809</v>
+        <v>11391</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1944</v>
+        <v>-4994</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1828,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28-APR-26</t>
+          <t>14-MAY-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1838,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6134</v>
+        <v>6397</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>6299</v>
+        <v>11391</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-165</v>
+        <v>-4994</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1873,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>14-MAY-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1887,29 +1905,3314 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6134</v>
+        <v>8249</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>6299</v>
+        <v>11391</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-165</v>
+        <v>-3142</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>14-MAY-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>14-MAY-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-1094</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>14-MAY-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-1094</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>15-MAY-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>15-MAY-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>15-MAY-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>15-MAY-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>15-MAY-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-2989</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>15-MAY-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-2989</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>16-MAY-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>16-MAY-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>19-MAY-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-2048</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>19-MAY-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-2048</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>21-MAY-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-1094</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>21-MAY-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1094</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>21-MAY-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>10577</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>21-MAY-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>10577</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-6411</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-6411</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>12499</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-3255</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>12499</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-3255</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>12075</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-3679</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>12075</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-3679</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>15011</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-743</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>15011</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-743</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>02-JUN-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-4363</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>02-JUN-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>11391</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-4363</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>02-JUN-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>02-JUN-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-5457</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-5457</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>15754</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>10199</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-547</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>10199</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-547</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-449</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-449</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>16-JUN-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>16-JUN-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>9343</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-814</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>23-JUN-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>23-JUN-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>10157</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>10199</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-547</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>10199</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-547</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-449</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-449</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7168</v>
+        <v>5650</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8838</v>
+        <v>6242</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1670</v>
+        <v>-592</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7168</v>
+        <v>5622</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8838</v>
+        <v>6242</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1670</v>
+        <v>-620</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7716</v>
+        <v>5650</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8838</v>
+        <v>6242</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1122</v>
+        <v>-592</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7716</v>
+        <v>5650</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8838</v>
+        <v>6242</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1122</v>
+        <v>-592</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-117</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8249</v>
+        <v>5650</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8403</v>
+        <v>6242</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-154</v>
+        <v>-592</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8249</v>
+        <v>5650</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8403</v>
+        <v>6242</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-154</v>
+        <v>-592</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8664</v>
+        <v>6087</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9567</v>
+        <v>6242</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-903</v>
+        <v>-155</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8664</v>
+        <v>6115</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9567</v>
+        <v>6242</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-903</v>
+        <v>-127</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7168</v>
+        <v>5650</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7182</v>
+        <v>6242</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-14</v>
+        <v>-592</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,27 +946,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7168</v>
+        <v>5622</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7182</v>
+        <v>6242</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-14</v>
+        <v>-620</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,27 +991,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7716</v>
+        <v>5650</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8403</v>
+        <v>6242</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-687</v>
+        <v>-592</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7716</v>
+        <v>5622</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8403</v>
+        <v>6242</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-687</v>
+        <v>-620</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9553</v>
+        <v>5650</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8403</v>
+        <v>6242</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1150</v>
+        <v>-592</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9553</v>
+        <v>5650</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8403</v>
+        <v>6242</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1150</v>
+        <v>-592</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>10-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-117</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6513</v>
+        <v>5650</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7182</v>
+        <v>6242</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-669</v>
+        <v>-592</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10-APR-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6513</v>
+        <v>11751</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7182</v>
+        <v>9736</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-669</v>
+        <v>2015</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8249</v>
+        <v>8721</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8992</v>
+        <v>8736</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-743</v>
+        <v>-15</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8249</v>
+        <v>9835</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>8992</v>
+        <v>8736</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-743</v>
+        <v>1099</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11012</v>
+        <v>9835</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8992</v>
+        <v>7735</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2020</v>
+        <v>2100</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11012</v>
+        <v>9835</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8992</v>
+        <v>7735</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2020</v>
+        <v>2100</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>12-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,22 +1455,22 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6397</v>
+        <v>9722</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10157</v>
+        <v>9736</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-3760</v>
+        <v>-14</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12-MAY-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6397</v>
+        <v>10567</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10157</v>
+        <v>11737</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-3760</v>
+        <v>-1170</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12-MAY-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8249</v>
+        <v>10624</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10157</v>
+        <v>11737</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1908</v>
+        <v>-1113</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>12-MAY-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>8249</v>
+        <v>11187</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>10157</v>
+        <v>11737</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1908</v>
+        <v>-550</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>12-MAY-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,26 +1635,26 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10297</v>
+        <v>9835</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>10157</v>
+        <v>11737</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>140</v>
+        <v>-1902</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>12-MAY-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>10297</v>
+        <v>11497</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>10157</v>
+        <v>11737</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>140</v>
+        <v>-240</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1725,26 +1725,26 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6397</v>
+        <v>8721</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11391</v>
+        <v>9736</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4994</v>
+        <v>-1015</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1770,26 +1770,26 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6397</v>
+        <v>8721</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11391</v>
+        <v>9736</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4994</v>
+        <v>-1015</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8249</v>
+        <v>9835</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11391</v>
+        <v>9736</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-3142</v>
+        <v>99</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,26 +1856,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8249</v>
+        <v>8721</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-3142</v>
+        <v>-2015</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>10297</v>
+        <v>10229</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1094</v>
+        <v>-507</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>10297</v>
+        <v>9722</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11391</v>
+        <v>11737</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1094</v>
+        <v>-2015</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8249</v>
+        <v>10201</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11391</v>
+        <v>11737</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-3142</v>
+        <v>-1536</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>8249</v>
+        <v>11187</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11391</v>
+        <v>11737</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-3142</v>
+        <v>-550</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8249</v>
+        <v>11215</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11391</v>
+        <v>11737</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-3142</v>
+        <v>-522</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>8249</v>
+        <v>11497</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11391</v>
+        <v>11737</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-3142</v>
+        <v>-240</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8402</v>
+        <v>11751</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11391</v>
+        <v>11737</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-2989</v>
+        <v>14</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8402</v>
+        <v>8214</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-2989</v>
+        <v>-2522</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>16-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,23 +2261,23 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8249</v>
+        <v>9015</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-3142</v>
+        <v>-1721</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>16-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>8249</v>
+        <v>9835</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-3142</v>
+        <v>-901</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9343</v>
+        <v>10624</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-2048</v>
+        <v>-112</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>9343</v>
+        <v>9095</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-2048</v>
+        <v>-1641</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>10</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>10297</v>
+        <v>10229</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1094</v>
+        <v>-507</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10297</v>
+        <v>10624</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>11391</v>
+        <v>10736</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1094</v>
+        <v>-112</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10577</v>
+        <v>10201</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11391</v>
+        <v>9736</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-814</v>
+        <v>465</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10577</v>
+        <v>9722</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11391</v>
+        <v>9736</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-814</v>
+        <v>-14</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>30</v>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>9343</v>
+        <v>9835</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>15754</v>
+        <v>9736</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-6411</v>
+        <v>99</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>46</v>
@@ -2642,9 +2642,9 @@
       <c r="I48" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>9343</v>
+        <v>9835</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15754</v>
+        <v>9736</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-6411</v>
+        <v>99</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2687,9 +2687,9 @@
       <c r="I49" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>12499</v>
+        <v>10624</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15754</v>
+        <v>11737</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-3255</v>
+        <v>-1113</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>30</v>
@@ -2732,9 +2732,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>12499</v>
+        <v>11187</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>15754</v>
+        <v>11737</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-3255</v>
+        <v>-550</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>30</v>
@@ -2777,9 +2777,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>13103</v>
+        <v>9835</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>15754</v>
+        <v>9736</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-2651</v>
+        <v>99</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>13103</v>
+        <v>9539</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>15754</v>
+        <v>10736</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-2651</v>
+        <v>-1197</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>12075</v>
+        <v>9722</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>15754</v>
+        <v>10736</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-3679</v>
+        <v>-1014</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>30</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>12075</v>
+        <v>10229</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>15754</v>
+        <v>10736</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-3679</v>
+        <v>-507</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>30</v>
@@ -2957,9 +2957,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>13103</v>
+        <v>9835</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>15754</v>
+        <v>10736</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-2651</v>
+        <v>-901</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>13103</v>
+        <v>10229</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>15754</v>
+        <v>10736</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-2651</v>
+        <v>-507</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>30</v>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>13103</v>
+        <v>9095</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>15754</v>
+        <v>11737</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-2651</v>
+        <v>-2642</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>13103</v>
+        <v>10624</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>15754</v>
+        <v>11737</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-2651</v>
+        <v>-1113</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>30</v>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>15011</v>
+        <v>10624</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>15754</v>
+        <v>11737</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-743</v>
+        <v>-1113</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>30</v>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>15011</v>
+        <v>9835</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>15754</v>
+        <v>9736</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-743</v>
+        <v>99</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>11391</v>
+        <v>9722</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-4363</v>
+        <v>-9004</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11391</v>
+        <v>9835</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-4363</v>
+        <v>-8891</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3345,13 +3345,13 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>13103</v>
+        <v>10229</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-2651</v>
+        <v>-8497</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>30</v>
@@ -3362,9 +3362,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>13103</v>
+        <v>9015</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-2651</v>
+        <v>-9711</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10297</v>
+        <v>9835</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-5457</v>
+        <v>-8891</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>46</v>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,26 +3476,26 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10297</v>
+        <v>11187</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-5457</v>
+        <v>-7539</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,30 +3521,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>13103</v>
+        <v>9095</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-2651</v>
+        <v>-9631</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>13103</v>
+        <v>12836</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-2651</v>
+        <v>-5890</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3587,9 +3587,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>13103</v>
+        <v>12836</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-2651</v>
+        <v>-5890</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3632,9 +3632,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>13103</v>
+        <v>9835</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-2651</v>
+        <v>-8891</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>13103</v>
+        <v>12836</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-2651</v>
+        <v>-5890</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3722,9 +3722,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>13103</v>
+        <v>9835</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>15754</v>
+        <v>18726</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-2651</v>
+        <v>-8891</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>10297</v>
+        <v>10567</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>10157</v>
+        <v>18726</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>140</v>
+        <v>-8159</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,30 +3836,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>10157</v>
+        <v>18726</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>140</v>
+        <v>-5890</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,30 +3881,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9343</v>
+        <v>9015</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>10157</v>
+        <v>18726</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-814</v>
+        <v>-9711</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>10</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3930,13 +3930,13 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9343</v>
+        <v>11215</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10157</v>
+        <v>18726</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-814</v>
+        <v>-7511</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>46</v>
@@ -3947,9 +3947,9 @@
       <c r="I77" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>8402</v>
+        <v>12836</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10157</v>
+        <v>18726</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-1755</v>
+        <v>-5890</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>30</v>
@@ -3992,9 +3992,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>8402</v>
+        <v>12836</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>10157</v>
+        <v>18726</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-1755</v>
+        <v>-5890</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>30</v>
@@ -4037,9 +4037,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>10199</v>
+        <v>12836</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>10746</v>
+        <v>18726</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-547</v>
+        <v>-5890</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>30</v>
@@ -4082,9 +4082,9 @@
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,26 +4106,26 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>10199</v>
+        <v>15053</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>10746</v>
+        <v>18726</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-547</v>
+        <v>-3673</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,30 +4151,30 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>10746</v>
+        <v>14231</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-449</v>
+        <v>-1395</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,30 +4196,30 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>10746</v>
+        <v>14231</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-449</v>
+        <v>-1395</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,30 +4241,30 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9343</v>
+        <v>14160</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-814</v>
+        <v>-71</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,30 +4286,30 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>9343</v>
+        <v>12836</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-814</v>
+        <v>-1395</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,26 +4331,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>140</v>
+        <v>-1395</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,26 +4376,26 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>140</v>
+        <v>-1395</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>8402</v>
+        <v>14217</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-1755</v>
+        <v>-14</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>30</v>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>8402</v>
+        <v>12836</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-1755</v>
+        <v>-1395</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>30</v>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,30 +4511,30 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>9343</v>
+        <v>14160</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-814</v>
+        <v>-71</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,30 +4556,30 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>9343</v>
+        <v>12836</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-814</v>
+        <v>-1395</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,30 +4601,30 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>10157</v>
+        <v>15724</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>140</v>
+        <v>-2888</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,26 +4646,26 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>10297</v>
+        <v>14217</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>10157</v>
+        <v>15724</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>140</v>
+        <v>-1507</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,26 +4691,26 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>10297</v>
+        <v>14217</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>10157</v>
+        <v>15724</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>140</v>
+        <v>-1507</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,30 +4736,30 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>10157</v>
+        <v>15724</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>140</v>
+        <v>-2888</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>8402</v>
+        <v>14160</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>10157</v>
+        <v>15724</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-1755</v>
+        <v>-1564</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>30</v>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>8402</v>
+        <v>12836</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>10157</v>
+        <v>14231</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-1755</v>
+        <v>-1395</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>30</v>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,30 +4871,30 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>10297</v>
+        <v>12836</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>10157</v>
+        <v>15724</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>140</v>
+        <v>-2888</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,26 +4916,26 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>10297</v>
+        <v>14217</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>10157</v>
+        <v>15724</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>140</v>
+        <v>-1507</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>10199</v>
+        <v>14217</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>10746</v>
+        <v>15724</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-547</v>
+        <v>-1507</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>30</v>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>10199</v>
+        <v>12836</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>10746</v>
+        <v>14231</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-547</v>
+        <v>-1395</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>30</v>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,30 +5051,30 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>10297</v>
+        <v>14160</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>10746</v>
+        <v>14231</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-449</v>
+        <v>-71</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,33 +5096,1698 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-811</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
-        <v>10297</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>10746</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>-449</v>
-      </c>
-      <c r="G103" s="2" t="n">
+      <c r="D109" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G109" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H103" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>16570</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-2156</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>16649</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-2077</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>13385</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-5341</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>9015</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-9711</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>10680</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>-8046</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>9095</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-9631</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>10680</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>-8046</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>10680</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>944</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>10680</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>944</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>1479</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -585,10 +603,10 @@
         <v>5622</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6242</v>
+        <v>6735</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-620</v>
+        <v>-1113</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -630,10 +648,10 @@
         <v>5650</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6242</v>
+        <v>6735</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-592</v>
+        <v>-1085</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -675,10 +693,10 @@
         <v>5650</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6242</v>
+        <v>6735</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-592</v>
+        <v>-1085</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -720,10 +738,10 @@
         <v>5650</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6242</v>
+        <v>6735</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-592</v>
+        <v>-1085</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -748,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5650</v>
+        <v>5622</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>6242</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-592</v>
+        <v>-620</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -838,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6115</v>
+        <v>5650</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>6242</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-127</v>
+        <v>-592</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-117</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -928,27 +946,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5622</v>
+        <v>5650</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>6242</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-620</v>
+        <v>-592</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,12 +991,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1018,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1028,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5622</v>
+        <v>6115</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6242</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-620</v>
+        <v>-127</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1073,7 +1091,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1108,27 +1126,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5650</v>
+        <v>5622</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>6242</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-592</v>
+        <v>-620</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1153,27 +1171,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5650</v>
+        <v>6087</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>6242</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-592</v>
+        <v>-155</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1198,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1208,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6087</v>
+        <v>5622</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>6242</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-155</v>
+        <v>-620</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1243,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1253,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11751</v>
+        <v>5650</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9736</v>
+        <v>6242</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2015</v>
+        <v>-592</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1288,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1298,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11497</v>
+        <v>5650</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11737</v>
+        <v>6242</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-240</v>
+        <v>-592</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1333,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1343,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-117</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9835</v>
+        <v>5650</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7735</v>
+        <v>6242</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2100</v>
+        <v>-592</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1378,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1388,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9835</v>
+        <v>6087</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8736</v>
+        <v>6242</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1099</v>
+        <v>-155</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1423,43 +1441,5803 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>11751</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>7735</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>8736</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>13-JUN-26</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-811</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D26" s="2" t="n">
         <v>9835</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E26" s="2" t="n">
         <v>7735</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>2100</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>9722</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>10567</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-1170</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>10624</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-1902</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>10624</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>23-JUN-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>8721</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-1015</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>8721</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-1015</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>8721</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>9095</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-1641</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>10229</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>9722</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>10201</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-1536</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-522</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>11497</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-240</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>11751</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>8214</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-2522</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>9015</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-1721</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-901</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>10229</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>8721</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>9095</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-1641</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>10229</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>10624</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>10201</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>9722</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>9722</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>9095</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-2642</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>10567</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-1170</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>10624</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>9539</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-1197</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>9722</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-1014</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>10229</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>8721</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>9015</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-1721</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-901</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>10229</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>10736</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>10567</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-1170</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>10624</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>10624</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>9722</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-9004</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-8891</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>10229</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-8497</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>9722</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-9004</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-8891</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>9095</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-9631</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>12667</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-6059</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-5890</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-5890</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-8891</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-5890</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>9835</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-8891</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>10567</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-8159</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-5890</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>9015</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-9711</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-5890</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>12667</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-6059</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-5890</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-5890</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>15053</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-3673</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>14160</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-71</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>14217</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>14160</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-71</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-2888</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>14217</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-1507</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>14217</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-1507</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-2888</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>14160</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-1564</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>20-AUG-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-2888</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>14217</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-1507</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>22-AUG-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>14217</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>15724</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-1507</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>14160</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-71</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>12836</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-1395</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>16569</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>-2157</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>15062</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>-7511</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>12244</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>-6482</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>9539</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>-9187</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>9539</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>-9187</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>11187</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>18726</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>-7539</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>11215</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>9736</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>1479</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-592</v>
+        <v>-585</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5622</v>
+        <v>5564</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6735</v>
+        <v>7656</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1113</v>
+        <v>-2092</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6735</v>
+        <v>7656</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1085</v>
+        <v>-2064</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6735</v>
+        <v>7656</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1085</v>
+        <v>-2064</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6735</v>
+        <v>7656</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1085</v>
+        <v>-2064</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5622</v>
+        <v>5592</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-620</v>
+        <v>-585</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-592</v>
+        <v>-585</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5650</v>
+        <v>6052</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-592</v>
+        <v>-125</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-592</v>
+        <v>-585</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,27 +946,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5650</v>
+        <v>5564</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-592</v>
+        <v>-613</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,12 +991,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-592</v>
+        <v>-585</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6115</v>
+        <v>5564</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-127</v>
+        <v>-613</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5650</v>
+        <v>5592</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-592</v>
+        <v>-585</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1126,27 +1126,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5622</v>
+        <v>5592</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-620</v>
+        <v>-585</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1171,27 +1171,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-117</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6087</v>
+        <v>5592</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-155</v>
+        <v>-585</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5622</v>
+        <v>6024</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6242</v>
+        <v>6177</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-620</v>
+        <v>-153</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5650</v>
+        <v>6875</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6242</v>
+        <v>7656</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-592</v>
+        <v>-781</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5650</v>
+        <v>6875</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6242</v>
+        <v>7167</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-592</v>
+        <v>-292</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5650</v>
+        <v>10459</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>6242</v>
+        <v>10626</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-592</v>
+        <v>-167</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6087</v>
+        <v>11630</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6242</v>
+        <v>9636</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-155</v>
+        <v>1994</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>12836</v>
+        <v>11379</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14231</v>
+        <v>11616</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1395</v>
+        <v>-237</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11751</v>
+        <v>9622</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9736</v>
+        <v>10626</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2015</v>
+        <v>-1004</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9835</v>
+        <v>9733</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>7735</v>
+        <v>10626</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2100</v>
+        <v>-893</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9835</v>
+        <v>10514</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8736</v>
+        <v>10626</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1099</v>
+        <v>-112</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9835</v>
+        <v>9622</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>7735</v>
+        <v>9636</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2100</v>
+        <v>-14</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9722</v>
+        <v>9733</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>9736</v>
+        <v>9636</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-14</v>
+        <v>97</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10567</v>
+        <v>9733</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11737</v>
+        <v>9636</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1170</v>
+        <v>97</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>10624</v>
+        <v>9733</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11737</v>
+        <v>8646</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1113</v>
+        <v>1087</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>11187</v>
+        <v>9733</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11737</v>
+        <v>7656</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-550</v>
+        <v>2077</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>9835</v>
+        <v>8922</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11737</v>
+        <v>11616</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1902</v>
+        <v>-2694</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>10624</v>
+        <v>9441</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11737</v>
+        <v>11616</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1113</v>
+        <v>-2175</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8721</v>
+        <v>9622</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9736</v>
+        <v>11616</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1015</v>
+        <v>-1994</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8721</v>
+        <v>11072</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9736</v>
+        <v>11616</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1015</v>
+        <v>-544</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>9835</v>
+        <v>10459</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>9736</v>
+        <v>11616</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>99</v>
+        <v>-1157</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8721</v>
+        <v>10514</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-2015</v>
+        <v>-1102</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>9095</v>
+        <v>11072</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1641</v>
+        <v>-544</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10229</v>
+        <v>9733</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-507</v>
+        <v>-1883</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>9722</v>
+        <v>11379</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11737</v>
+        <v>11616</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-2015</v>
+        <v>-237</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>30</v>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>10201</v>
+        <v>8632</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11737</v>
+        <v>9636</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1536</v>
+        <v>-1004</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>11187</v>
+        <v>8632</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11737</v>
+        <v>9636</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-550</v>
+        <v>-1004</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>30</v>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>11215</v>
+        <v>9733</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11737</v>
+        <v>9636</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-522</v>
+        <v>97</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>11497</v>
+        <v>8632</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11737</v>
+        <v>10626</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-240</v>
+        <v>-1994</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>30</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>11751</v>
+        <v>9001</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11737</v>
+        <v>10626</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>14</v>
+        <v>-1625</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>8214</v>
+        <v>10124</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10736</v>
+        <v>10626</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-2522</v>
+        <v>-502</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>9015</v>
+        <v>9622</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1721</v>
+        <v>-1994</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>9835</v>
+        <v>10096</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-901</v>
+        <v>-1520</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>46</v>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10229</v>
+        <v>11072</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-507</v>
+        <v>-544</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>30</v>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>8721</v>
+        <v>11100</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-2015</v>
+        <v>-516</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>30</v>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>9095</v>
+        <v>11379</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1641</v>
+        <v>-237</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>10229</v>
+        <v>11630</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-507</v>
+        <v>14</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10624</v>
+        <v>8130</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>10736</v>
+        <v>10626</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-112</v>
+        <v>-2496</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>10201</v>
+        <v>8922</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9736</v>
+        <v>10626</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>465</v>
+        <v>-1704</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>9722</v>
+        <v>9733</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>9736</v>
+        <v>10626</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-14</v>
+        <v>-893</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>9835</v>
+        <v>10124</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>9736</v>
+        <v>10626</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>99</v>
+        <v>-502</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>9722</v>
+        <v>8632</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9736</v>
+        <v>10626</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-14</v>
+        <v>-1994</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>30</v>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,26 +3026,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>9835</v>
+        <v>10124</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>9736</v>
+        <v>10626</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>99</v>
+        <v>-502</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>9095</v>
+        <v>10514</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>11737</v>
+        <v>10626</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-2642</v>
+        <v>-112</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>10567</v>
+        <v>10096</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>11737</v>
+        <v>9636</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-1170</v>
+        <v>460</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>10624</v>
+        <v>9622</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>11737</v>
+        <v>9636</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1113</v>
+        <v>-14</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>30</v>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11187</v>
+        <v>9733</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>11737</v>
+        <v>9636</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-550</v>
+        <v>97</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>9835</v>
+        <v>9622</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>9736</v>
+        <v>9636</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>99</v>
+        <v>-14</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3300,22 +3300,22 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>9539</v>
+        <v>9733</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10736</v>
+        <v>9636</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-1197</v>
+        <v>97</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,26 +3341,26 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>9722</v>
+        <v>9001</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-1014</v>
+        <v>-2615</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10229</v>
+        <v>10459</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-507</v>
+        <v>-1157</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>30</v>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>8721</v>
+        <v>10514</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-2015</v>
+        <v>-1102</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>30</v>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,26 +3476,26 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>9015</v>
+        <v>11072</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>10736</v>
+        <v>11616</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-1721</v>
+        <v>-544</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9835</v>
+        <v>9733</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>10736</v>
+        <v>9636</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-901</v>
+        <v>97</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>46</v>
@@ -3542,9 +3542,9 @@
       <c r="I68" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,26 +3566,26 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>10229</v>
+        <v>9441</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>10736</v>
+        <v>10626</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-507</v>
+        <v>-1185</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10567</v>
+        <v>9622</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>11737</v>
+        <v>10626</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-1170</v>
+        <v>-1004</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10624</v>
+        <v>10124</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11737</v>
+        <v>10626</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-1113</v>
+        <v>-502</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>30</v>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>10624</v>
+        <v>8632</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>11737</v>
+        <v>10626</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-1113</v>
+        <v>-1994</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,26 +3746,26 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9835</v>
+        <v>8922</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>9736</v>
+        <v>10626</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>99</v>
+        <v>-1704</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9722</v>
+        <v>9733</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>18726</v>
+        <v>10626</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-9004</v>
+        <v>-893</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,30 +3836,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9835</v>
+        <v>10124</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18726</v>
+        <v>10626</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-8891</v>
+        <v>-502</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>10229</v>
+        <v>10459</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>18726</v>
+        <v>11616</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-8497</v>
+        <v>-1157</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>30</v>
@@ -3902,9 +3902,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9722</v>
+        <v>10514</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>18726</v>
+        <v>11616</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-9004</v>
+        <v>-1102</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>30</v>
@@ -3947,9 +3947,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,30 +3971,30 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>9835</v>
+        <v>10514</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>18726</v>
+        <v>11616</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-8891</v>
+        <v>-1102</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>11187</v>
+        <v>9733</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>18726</v>
+        <v>9636</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-7539</v>
+        <v>97</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,26 +4061,26 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9095</v>
+        <v>9622</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-9631</v>
+        <v>-8911</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,26 +4106,26 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>12667</v>
+        <v>9733</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-6059</v>
+        <v>-8800</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>12836</v>
+        <v>10124</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-5890</v>
+        <v>-8409</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>30</v>
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,26 +4196,26 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>12836</v>
+        <v>8922</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-5890</v>
+        <v>-9611</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,26 +4241,26 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9835</v>
+        <v>9622</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-8891</v>
+        <v>-8911</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,26 +4286,26 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>12836</v>
+        <v>9733</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-5890</v>
+        <v>-8800</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,26 +4331,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>9835</v>
+        <v>11072</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-8891</v>
+        <v>-7461</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,26 +4376,26 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>10567</v>
+        <v>9001</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-8159</v>
+        <v>-9532</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>12836</v>
+        <v>12536</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-5890</v>
+        <v>-5997</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>30</v>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,26 +4466,26 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>9015</v>
+        <v>12704</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-9711</v>
+        <v>-5829</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>11215</v>
+        <v>12704</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-7511</v>
+        <v>-5829</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>30</v>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>11215</v>
+        <v>9733</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-7511</v>
+        <v>-8800</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>46</v>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-5890</v>
+        <v>-5829</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>30</v>
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,26 +4646,26 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>12667</v>
+        <v>9733</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-6059</v>
+        <v>-8800</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>12836</v>
+        <v>10459</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-5890</v>
+        <v>-8074</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>30</v>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-5890</v>
+        <v>-5829</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>30</v>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,30 +4781,30 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>15053</v>
+        <v>11100</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-3673</v>
+        <v>-7433</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,30 +4826,30 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>12836</v>
+        <v>11100</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>14231</v>
+        <v>18533</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-1395</v>
+        <v>-7433</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4875,13 +4875,13 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>14231</v>
+        <v>18533</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-1395</v>
+        <v>-5829</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>30</v>
@@ -4892,9 +4892,9 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>14160</v>
+        <v>12536</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>14231</v>
+        <v>18533</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-71</v>
+        <v>-5997</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>30</v>
@@ -4937,9 +4937,9 @@
       <c r="I99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14231</v>
+        <v>18533</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-1395</v>
+        <v>-5829</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>30</v>
@@ -4982,9 +4982,9 @@
       <c r="I100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>14231</v>
+        <v>18533</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-1395</v>
+        <v>-5829</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>30</v>
@@ -5027,9 +5027,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,26 +5051,26 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>12836</v>
+        <v>14898</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>14231</v>
+        <v>18533</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-1395</v>
+        <v>-3635</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5100,13 +5100,13 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>14217</v>
+        <v>12704</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>14231</v>
+        <v>14084</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-14</v>
+        <v>-1380</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>30</v>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5145,13 +5145,13 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>14231</v>
+        <v>14084</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-1395</v>
+        <v>-1380</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>30</v>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5190,13 +5190,13 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>14160</v>
+        <v>14015</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14231</v>
+        <v>14084</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-71</v>
+        <v>-69</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>30</v>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>14231</v>
+        <v>14084</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-1395</v>
+        <v>-1380</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>30</v>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>15724</v>
+        <v>14084</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-2888</v>
+        <v>-1380</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>30</v>
@@ -5297,9 +5297,9 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>14217</v>
+        <v>12704</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15724</v>
+        <v>14084</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-1507</v>
+        <v>-1380</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>30</v>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5370,13 +5370,13 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>14217</v>
+        <v>14070</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>15724</v>
+        <v>14084</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-1507</v>
+        <v>-14</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>30</v>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5415,13 +5415,13 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>15724</v>
+        <v>14084</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-2888</v>
+        <v>-1380</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>30</v>
@@ -5432,9 +5432,9 @@
       <c r="I110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5460,13 +5460,13 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>14160</v>
+        <v>14015</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>15724</v>
+        <v>14084</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-1564</v>
+        <v>-69</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>30</v>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5505,13 +5505,13 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14231</v>
+        <v>15563</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-1395</v>
+        <v>-2859</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>30</v>
@@ -5522,9 +5522,9 @@
       <c r="I112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>15724</v>
+        <v>15563</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-2888</v>
+        <v>-2859</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>30</v>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>14217</v>
+        <v>14070</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>15724</v>
+        <v>15563</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-1507</v>
+        <v>-1493</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>30</v>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>22-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>14217</v>
+        <v>14070</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>15724</v>
+        <v>15563</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-1507</v>
+        <v>-1493</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>30</v>
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14231</v>
+        <v>15563</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-1395</v>
+        <v>-2859</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>30</v>
@@ -5702,9 +5702,9 @@
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>14160</v>
+        <v>14015</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14231</v>
+        <v>15563</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-71</v>
+        <v>-1548</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>30</v>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5775,13 +5775,13 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>14231</v>
+        <v>14084</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-1395</v>
+        <v>-1380</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>30</v>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5820,13 +5820,13 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>12836</v>
+        <v>12704</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>14231</v>
+        <v>15563</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-1395</v>
+        <v>-2859</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>30</v>
@@ -5837,9 +5837,9 @@
       <c r="I119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5865,13 +5865,13 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>12836</v>
+        <v>14070</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>14231</v>
+        <v>15563</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-1395</v>
+        <v>-1493</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>30</v>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>29-AUG-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5910,13 +5910,13 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>12836</v>
+        <v>14070</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>14231</v>
+        <v>15563</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-1395</v>
+        <v>-1493</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>30</v>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5955,13 +5955,13 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>11187</v>
+        <v>12704</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>18726</v>
+        <v>14084</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-7539</v>
+        <v>-1380</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>30</v>
@@ -5972,9 +5972,9 @@
       <c r="I122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6000,13 +6000,13 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>11215</v>
+        <v>14015</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>18726</v>
+        <v>14084</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-7511</v>
+        <v>-69</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>30</v>
@@ -6017,9 +6017,9 @@
       <c r="I123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J123" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,30 +6041,30 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>15062</v>
+        <v>12704</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>18726</v>
+        <v>14084</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-3664</v>
+        <v>-1380</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J124" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>11187</v>
+        <v>12704</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>18726</v>
+        <v>14084</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-7539</v>
+        <v>-1380</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>30</v>
@@ -6107,9 +6107,9 @@
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,30 +6131,30 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>15062</v>
+        <v>12704</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>18726</v>
+        <v>14084</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-3664</v>
+        <v>-1380</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J126" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>29-AUG-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>11187</v>
+        <v>12704</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>18726</v>
+        <v>14084</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-7539</v>
+        <v>-1380</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>30</v>
@@ -6197,9 +6197,9 @@
       <c r="I127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>11187</v>
+        <v>11072</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-7539</v>
+        <v>-7461</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>30</v>
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>11187</v>
+        <v>11100</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-7539</v>
+        <v>-7433</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>30</v>
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>15062</v>
+        <v>14907</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-3664</v>
+        <v>-3626</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>46</v>
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6360,13 +6360,13 @@
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>11187</v>
+        <v>11072</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-7539</v>
+        <v>-7461</v>
       </c>
       <c r="G131" s="2" t="n">
         <v>30</v>
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,26 +6401,26 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>11215</v>
+        <v>14907</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-7511</v>
+        <v>-3626</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,26 +6446,26 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>15062</v>
+        <v>11072</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-3664</v>
+        <v>-7461</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H133" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>11187</v>
+        <v>11072</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-7539</v>
+        <v>-7461</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>30</v>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,26 +6536,26 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>15062</v>
+        <v>11072</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-3664</v>
+        <v>-7461</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,30 +6581,30 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>16569</v>
+        <v>14907</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-2157</v>
+        <v>-3626</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6626,17 +6626,17 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>11187</v>
+        <v>11072</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-7539</v>
+        <v>-7461</v>
       </c>
       <c r="G137" s="2" t="n">
         <v>30</v>
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6671,17 +6671,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>11187</v>
+        <v>11100</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-7539</v>
+        <v>-7433</v>
       </c>
       <c r="G138" s="2" t="n">
         <v>30</v>
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,26 +6716,26 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>11187</v>
+        <v>14907</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-7539</v>
+        <v>-3626</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,26 +6761,26 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>15062</v>
+        <v>11072</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-3664</v>
+        <v>-7461</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H140" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,26 +6806,26 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>11187</v>
+        <v>14907</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-7539</v>
+        <v>-3626</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,30 +6851,30 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>11215</v>
+        <v>16399</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-7511</v>
+        <v>-2134</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6896,30 +6896,30 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>12244</v>
+        <v>11072</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-6482</v>
+        <v>-7461</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6941,26 +6941,26 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>9539</v>
+        <v>11072</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-9187</v>
+        <v>-7461</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>11187</v>
+        <v>11072</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-7539</v>
+        <v>-7461</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>30</v>
@@ -7021,7 +7021,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7031,26 +7031,26 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>11187</v>
+        <v>14907</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>-7539</v>
+        <v>-3626</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H146" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7076,17 +7076,17 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>11187</v>
+        <v>11072</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>-7539</v>
+        <v>-7461</v>
       </c>
       <c r="G147" s="2" t="n">
         <v>30</v>
@@ -7111,7 +7111,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7121,26 +7121,26 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>9539</v>
+        <v>11100</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>-9187</v>
+        <v>-7433</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H148" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7166,30 +7166,30 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>11187</v>
+        <v>12118</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>18726</v>
+        <v>18533</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>-7539</v>
+        <v>-6415</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H149" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7201,43 +7201,403 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>8922</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>-9611</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>9441</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>-9092</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>11072</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>-7461</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>9001</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>-9532</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>11072</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>-7461</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>11072</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>-7461</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>9441</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>-9092</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>11072</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>18533</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>-7461</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-811</t>
         </is>
       </c>
-      <c r="D150" s="2" t="n">
-        <v>11215</v>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>9736</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>1479</v>
-      </c>
-      <c r="G150" s="2" t="n">
+      <c r="D158" s="2" t="n">
+        <v>11100</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>9636</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="G158" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H150" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I150" s="2" t="n">
+      <c r="H158" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I158" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,27 +541,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5592</v>
+        <v>4894</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6177</v>
+        <v>4908</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-585</v>
+        <v>-14</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5564</v>
+        <v>4894</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7656</v>
+        <v>4908</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2092</v>
+        <v>-14</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5592</v>
+        <v>6024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7656</v>
+        <v>6177</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2064</v>
+        <v>-153</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5592</v>
+        <v>11602</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7656</v>
+        <v>10598</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2064</v>
+        <v>1004</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5592</v>
+        <v>11602</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7656</v>
+        <v>9594</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2064</v>
+        <v>2008</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5592</v>
+        <v>11072</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6177</v>
+        <v>12564</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-585</v>
+        <v>-1492</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5592</v>
+        <v>11351</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6177</v>
+        <v>12564</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-585</v>
+        <v>-1213</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6052</v>
+        <v>13805</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6177</v>
+        <v>11588</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-125</v>
+        <v>2217</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5592</v>
+        <v>8618</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6177</v>
+        <v>9622</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-585</v>
+        <v>-1004</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,40 +946,40 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5564</v>
+        <v>9733</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6177</v>
+        <v>9622</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-613</v>
+        <v>111</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,40 +991,40 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5592</v>
+        <v>9733</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6177</v>
+        <v>8632</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-585</v>
+        <v>1101</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5564</v>
+        <v>8835</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6177</v>
+        <v>11588</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-613</v>
+        <v>-2753</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5592</v>
+        <v>8835</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6177</v>
+        <v>11546</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-585</v>
+        <v>-2711</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5592</v>
+        <v>9441</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6177</v>
+        <v>11588</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-585</v>
+        <v>-2147</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5592</v>
+        <v>9441</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6177</v>
+        <v>11546</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-585</v>
+        <v>-2105</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6024</v>
+        <v>9580</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6177</v>
+        <v>11588</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-153</v>
+        <v>-2008</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6875</v>
+        <v>9580</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7656</v>
+        <v>11546</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-781</v>
+        <v>-1966</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6875</v>
+        <v>11044</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7167</v>
+        <v>11588</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-292</v>
+        <v>-544</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10459</v>
+        <v>11044</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10626</v>
+        <v>11546</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-167</v>
+        <v>-502</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11630</v>
+        <v>10431</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9636</v>
+        <v>11588</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1994</v>
+        <v>-1157</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11379</v>
+        <v>10486</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11616</v>
+        <v>11588</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-237</v>
+        <v>-1102</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9622</v>
+        <v>11072</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10626</v>
+        <v>11588</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1004</v>
+        <v>-516</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1548,10 +1548,10 @@
         <v>9733</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10626</v>
+        <v>11588</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-893</v>
+        <v>-1855</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10514</v>
+        <v>11351</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>10626</v>
+        <v>11588</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-112</v>
+        <v>-237</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
+        <v>8618</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>9622</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>9636</v>
-      </c>
       <c r="F26" s="2" t="n">
-        <v>-14</v>
+        <v>-1004</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9733</v>
+        <v>9594</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>9636</v>
+        <v>9622</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>97</v>
+        <v>-28</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1728,10 +1728,10 @@
         <v>9733</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9636</v>
+        <v>9622</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9733</v>
+        <v>8618</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>8646</v>
+        <v>10598</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1087</v>
+        <v>-1980</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9733</v>
+        <v>8914</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7656</v>
+        <v>10598</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2077</v>
+        <v>-1684</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8922</v>
+        <v>10124</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11616</v>
+        <v>10598</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-2694</v>
+        <v>-474</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>9441</v>
+        <v>9594</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11616</v>
+        <v>11588</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-2175</v>
+        <v>-1994</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>9622</v>
+        <v>10082</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11616</v>
+        <v>11588</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1994</v>
+        <v>-1506</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1998,10 +1998,10 @@
         <v>11072</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11616</v>
+        <v>11588</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-544</v>
+        <v>-516</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>10459</v>
+        <v>11072</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11616</v>
+        <v>11588</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1157</v>
+        <v>-516</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>10514</v>
+        <v>11351</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11616</v>
+        <v>11588</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1102</v>
+        <v>-237</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>11072</v>
+        <v>12216</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11616</v>
+        <v>11588</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-544</v>
+        <v>628</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>9733</v>
+        <v>8116</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11616</v>
+        <v>10598</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1883</v>
+        <v>-2482</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11379</v>
+        <v>8835</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11616</v>
+        <v>10598</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-237</v>
+        <v>-1763</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8632</v>
+        <v>9733</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9636</v>
+        <v>10598</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1004</v>
+        <v>-865</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>8632</v>
+        <v>10124</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>9636</v>
+        <v>10598</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1004</v>
+        <v>-474</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>30</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9733</v>
+        <v>8618</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>9636</v>
+        <v>10598</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>97</v>
+        <v>-1980</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>8632</v>
+        <v>8914</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1994</v>
+        <v>-1684</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>9001</v>
+        <v>10124</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1625</v>
+        <v>-474</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10124</v>
+        <v>10486</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-502</v>
+        <v>-112</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
+        <v>10082</v>
+      </c>
+      <c r="E46" s="2" t="n">
         <v>9622</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>11616</v>
-      </c>
       <c r="F46" s="2" t="n">
-        <v>-1994</v>
+        <v>460</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10096</v>
+        <v>9594</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11616</v>
+        <v>9622</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1520</v>
+        <v>-28</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>11072</v>
+        <v>9733</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>11616</v>
+        <v>9622</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-544</v>
+        <v>111</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>11100</v>
+        <v>9594</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>11616</v>
+        <v>9622</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-516</v>
+        <v>-28</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>30</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11379</v>
+        <v>9733</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>11616</v>
+        <v>9622</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-237</v>
+        <v>111</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>11630</v>
+        <v>9733</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>11616</v>
+        <v>9622</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8130</v>
+        <v>9441</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-2496</v>
+        <v>-1157</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,30 +2846,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>8922</v>
+        <v>9594</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1704</v>
+        <v>-1004</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>9733</v>
+        <v>10124</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-893</v>
+        <v>-474</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>10124</v>
+        <v>8618</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-502</v>
+        <v>-1980</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>30</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>8632</v>
+        <v>9733</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1994</v>
+        <v>-865</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
         <v>10124</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>10626</v>
+        <v>10598</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-502</v>
+        <v>-474</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>30</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>10514</v>
+        <v>10431</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>10626</v>
+        <v>11588</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-112</v>
+        <v>-1157</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>30</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>10096</v>
+        <v>10486</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>9636</v>
+        <v>11588</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>460</v>
+        <v>-1102</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>9622</v>
+        <v>10486</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>9636</v>
+        <v>11588</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-14</v>
+        <v>-1102</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>30</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3213,10 +3213,10 @@
         <v>9733</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>9636</v>
+        <v>9622</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>9622</v>
+        <v>9594</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>9636</v>
+        <v>18477</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-14</v>
+        <v>-8883</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>30</v>
@@ -3272,9 +3272,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3303,10 +3303,10 @@
         <v>9733</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>9636</v>
+        <v>18477</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>97</v>
+        <v>-8744</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3317,9 +3317,9 @@
       <c r="I63" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>9001</v>
+        <v>10124</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>11616</v>
+        <v>18477</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-2615</v>
+        <v>-8353</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10459</v>
+        <v>8835</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11616</v>
+        <v>18477</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-1157</v>
+        <v>-9642</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10514</v>
+        <v>9594</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11616</v>
+        <v>18477</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-1102</v>
+        <v>-8883</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>30</v>
@@ -3452,9 +3452,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,30 +3476,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>11072</v>
+        <v>9733</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11616</v>
+        <v>18477</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-544</v>
+        <v>-8744</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,30 +3521,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9733</v>
+        <v>11072</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>9636</v>
+        <v>18477</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>97</v>
+        <v>-7405</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9441</v>
+        <v>12509</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>10626</v>
+        <v>18477</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-1185</v>
+        <v>-5968</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9622</v>
+        <v>12676</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>10626</v>
+        <v>18477</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-1004</v>
+        <v>-5801</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3632,9 +3632,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10124</v>
+        <v>12676</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>10626</v>
+        <v>18477</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-502</v>
+        <v>-5801</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>30</v>
@@ -3677,9 +3677,9 @@
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,30 +3701,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>8632</v>
+        <v>9733</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10626</v>
+        <v>18477</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-1994</v>
+        <v>-8744</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>8922</v>
+        <v>12676</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>10626</v>
+        <v>18477</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-1704</v>
+        <v>-5801</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3798,10 +3798,10 @@
         <v>9733</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>10626</v>
+        <v>18477</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-893</v>
+        <v>-8744</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>46</v>
@@ -3812,9 +3812,9 @@
       <c r="I74" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>10124</v>
+        <v>10431</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>10626</v>
+        <v>18477</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-502</v>
+        <v>-8046</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>30</v>
@@ -3857,9 +3857,9 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>10459</v>
+        <v>12676</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>11616</v>
+        <v>18477</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-1157</v>
+        <v>-5801</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>30</v>
@@ -3902,9 +3902,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>10514</v>
+        <v>8835</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11616</v>
+        <v>18477</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-1102</v>
+        <v>-9642</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>10514</v>
+        <v>11072</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>11616</v>
+        <v>18477</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-1102</v>
+        <v>-7405</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>30</v>
@@ -3992,9 +3992,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4020,13 +4020,13 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9733</v>
+        <v>11086</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>9636</v>
+        <v>18477</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>97</v>
+        <v>-7391</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>46</v>
@@ -4037,9 +4037,9 @@
       <c r="I79" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9622</v>
+        <v>12676</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-8911</v>
+        <v>-5801</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>30</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,30 +4106,30 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>9733</v>
+        <v>12509</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-8800</v>
+        <v>-5968</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>10124</v>
+        <v>12676</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-8409</v>
+        <v>-5801</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>30</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,30 +4196,30 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>8922</v>
+        <v>14043</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-9611</v>
+        <v>-4434</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9622</v>
+        <v>12676</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-8911</v>
+        <v>-1367</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>30</v>
@@ -4262,9 +4262,9 @@
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,30 +4286,30 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>9733</v>
+        <v>12676</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-8800</v>
+        <v>-1367</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>11072</v>
+        <v>13987</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-7461</v>
+        <v>-56</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>30</v>
@@ -4352,9 +4352,9 @@
       <c r="I86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,30 +4376,30 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>9001</v>
+        <v>12676</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-9532</v>
+        <v>-1367</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>12536</v>
+        <v>12676</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-5997</v>
+        <v>-1367</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>30</v>
@@ -4442,9 +4442,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-5829</v>
+        <v>-1367</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>30</v>
@@ -4487,9 +4487,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-5829</v>
+        <v>-1367</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>30</v>
@@ -4532,9 +4532,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,30 +4556,30 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>9733</v>
+        <v>13987</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-8800</v>
+        <v>-56</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-5829</v>
+        <v>-1367</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>30</v>
@@ -4622,9 +4622,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,30 +4646,30 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>9733</v>
+        <v>12676</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>18533</v>
+        <v>15521</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-8800</v>
+        <v>-2845</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>10459</v>
+        <v>14043</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>18533</v>
+        <v>15521</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-8074</v>
+        <v>-1478</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>30</v>
@@ -4712,9 +4712,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4740,13 +4740,13 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>18533</v>
+        <v>15521</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-5829</v>
+        <v>-2845</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>30</v>
@@ -4757,9 +4757,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4785,13 +4785,13 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>11100</v>
+        <v>13987</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18533</v>
+        <v>15521</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-7433</v>
+        <v>-1534</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>30</v>
@@ -4802,9 +4802,9 @@
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,30 +4826,30 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>11100</v>
+        <v>12676</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-7433</v>
+        <v>-1367</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>18533</v>
+        <v>15521</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-5829</v>
+        <v>-2845</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>30</v>
@@ -4892,9 +4892,9 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>12536</v>
+        <v>14043</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>18533</v>
+        <v>15521</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-5997</v>
+        <v>-1478</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>30</v>
@@ -4937,9 +4937,9 @@
       <c r="I99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>12704</v>
+        <v>14043</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>18533</v>
+        <v>15521</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-5829</v>
+        <v>-1478</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>30</v>
@@ -4982,9 +4982,9 @@
       <c r="I100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-5829</v>
+        <v>-1367</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>30</v>
@@ -5027,9 +5027,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,30 +5051,30 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>14898</v>
+        <v>13987</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>18533</v>
+        <v>14043</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-3635</v>
+        <v>-56</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>14084</v>
+        <v>14043</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-1380</v>
+        <v>-1367</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>30</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>12704</v>
+        <v>12676</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>14084</v>
+        <v>14043</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-1380</v>
+        <v>-1367</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>30</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>29-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>14015</v>
+        <v>12676</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14084</v>
+        <v>14043</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-69</v>
+        <v>-1367</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>30</v>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-1380</v>
+        <v>-7405</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>30</v>
@@ -5252,9 +5252,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-1380</v>
+        <v>-7405</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>30</v>
@@ -5297,9 +5297,9 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,30 +5321,30 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>12704</v>
+        <v>14879</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-1380</v>
+        <v>-3598</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5370,13 +5370,13 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>14070</v>
+        <v>11072</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-14</v>
+        <v>-7405</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>30</v>
@@ -5387,9 +5387,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,30 +5411,30 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>12704</v>
+        <v>14879</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-1380</v>
+        <v>-3598</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>14015</v>
+        <v>11072</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-69</v>
+        <v>-7405</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>30</v>
@@ -5477,9 +5477,9 @@
       <c r="I111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-2859</v>
+        <v>-7405</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>30</v>
@@ -5522,9 +5522,9 @@
       <c r="I112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-2859</v>
+        <v>-7405</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>30</v>
@@ -5567,9 +5567,9 @@
       <c r="I113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,30 +5591,30 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>14070</v>
+        <v>14879</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-1493</v>
+        <v>-3598</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,17 +5636,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>14070</v>
+        <v>11072</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-1493</v>
+        <v>-7405</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>30</v>
@@ -5657,9 +5657,9 @@
       <c r="I115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-2859</v>
+        <v>-7405</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>30</v>
@@ -5702,9 +5702,9 @@
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,30 +5726,30 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>14015</v>
+        <v>14879</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-1548</v>
+        <v>-3598</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5775,13 +5775,13 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-1380</v>
+        <v>-7405</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>30</v>
@@ -5792,9 +5792,9 @@
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,30 +5816,30 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>12704</v>
+        <v>14879</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-2859</v>
+        <v>-3598</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>14070</v>
+        <v>11072</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-1493</v>
+        <v>-7405</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>30</v>
@@ -5882,9 +5882,9 @@
       <c r="I120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>22-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>14070</v>
+        <v>11072</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>15563</v>
+        <v>18477</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-1493</v>
+        <v>-7405</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>30</v>
@@ -5927,9 +5927,9 @@
       <c r="I121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,30 +5951,30 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>12704</v>
+        <v>16318</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-1380</v>
+        <v>-2159</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>14015</v>
+        <v>11072</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-69</v>
+        <v>-7405</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>30</v>
@@ -6017,9 +6017,9 @@
       <c r="I123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,30 +6041,30 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>12704</v>
+        <v>14879</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-1380</v>
+        <v>-3598</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-1380</v>
+        <v>-7405</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>30</v>
@@ -6107,9 +6107,9 @@
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>12704</v>
+        <v>11072</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-1380</v>
+        <v>-7405</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>30</v>
@@ -6152,9 +6152,9 @@
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>29-AUG-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,30 +6176,30 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>12704</v>
+        <v>12104</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>14084</v>
+        <v>18477</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-1380</v>
+        <v>-6373</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,30 +6221,30 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>11072</v>
+        <v>9441</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-7461</v>
+        <v>-9036</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>11100</v>
+        <v>11072</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-7433</v>
+        <v>-7405</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>30</v>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,30 +6311,30 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>14907</v>
+        <v>8914</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-3626</v>
+        <v>-9563</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6356,17 +6356,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
         <v>11072</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-7461</v>
+        <v>-7405</v>
       </c>
       <c r="G131" s="2" t="n">
         <v>30</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,30 +6401,30 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>14907</v>
+        <v>11072</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-3626</v>
+        <v>-7405</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,30 +6446,30 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>11072</v>
+        <v>9441</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-7461</v>
+        <v>-9036</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H133" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
         <v>11072</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>18533</v>
+        <v>18477</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-7461</v>
+        <v>-7405</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>30</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,1068 +6536,33 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>11072</v>
+        <v>11086</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>18533</v>
+        <v>9622</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-7461</v>
+        <v>1464</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>05-SEP-26</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
-        <v>14907</v>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>-3626</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>08-SEP-26</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>08-SEP-26</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-122</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="n">
-        <v>11100</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>-7433</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>08-SEP-26</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>14907</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>-3626</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>14907</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>-3626</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J141" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-599</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>16399</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>-2134</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>12-SEP-26</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>12-SEP-26</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>14907</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>-3626</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J146" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-122</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>11100</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>-7433</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="n">
-        <v>12118</v>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>-6415</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-599</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="n">
-        <v>8922</v>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>-9611</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J150" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="n">
-        <v>9441</v>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>-9092</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J151" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-599</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="n">
-        <v>9001</v>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>-9532</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J153" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="n">
-        <v>9441</v>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>-9092</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J156" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="n">
-        <v>11072</v>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>18533</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>-7461</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="n">
-        <v>11100</v>
-      </c>
-      <c r="E158" s="2" t="n">
-        <v>9636</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>1464</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1027,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,13 +1032,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>14226</v>
+        <v>10645</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14240</v>
+        <v>10758</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-14</v>
+        <v>-113</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1082,26 +1073,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11791</v>
+        <v>9239</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9753</v>
+        <v>10758</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2038</v>
+        <v>-1519</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1108,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1118,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11239</v>
+        <v>10277</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12754</v>
+        <v>10758</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1515</v>
+        <v>-481</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1162,7 +1153,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,26 +1163,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11522</v>
+        <v>12386</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12754</v>
+        <v>10758</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1232</v>
+        <v>1628</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1198,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,17 +1208,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11522</v>
+        <v>11239</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11749</v>
+        <v>12754</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-227</v>
+        <v>-1515</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1252,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,26 +1253,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>14014</v>
+        <v>11522</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11749</v>
+        <v>12754</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2265</v>
+        <v>-1232</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1288,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,303 +1298,33 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8068</v>
+        <v>12683</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9753</v>
+        <v>12754</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1685</v>
+        <v>-71</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-122</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>8734</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>9753</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-1019</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>9116</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>9753</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-637</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>8068</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>7261</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>807</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-120</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>6738</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>7261</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-523</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>6978</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>7261</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-283</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>13-JUN-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>8068</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>7261</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>807</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,14 +551,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4940</v>
+        <v>4918</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>-42</v>
@@ -568,12 +586,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -582,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4940</v>
+        <v>4918</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>-42</v>
@@ -613,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-325</t>
+          <t>SM-979</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4940</v>
+        <v>4946</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-42</v>
+        <v>-14</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,24 +676,24 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4940</v>
+        <v>4918</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-42</v>
@@ -703,27 +721,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4968</v>
+        <v>4918</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-14</v>
+        <v>-42</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -758,14 +776,14 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-117</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4940</v>
+        <v>4918</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>-42</v>
@@ -803,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4940</v>
+        <v>4946</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-42</v>
+        <v>-14</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4940</v>
+        <v>6087</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4982</v>
+        <v>6243</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-42</v>
+        <v>-156</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4968</v>
+        <v>6947</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4982</v>
+        <v>7229</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-14</v>
+        <v>-282</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -928,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6115</v>
+        <v>10569</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6256</v>
+        <v>10724</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-141</v>
+        <v>-155</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -987,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6978</v>
+        <v>11189</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7261</v>
+        <v>12725</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-283</v>
+        <v>-1536</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1028,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10645</v>
+        <v>12655</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10758</v>
+        <v>12725</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-113</v>
+        <v>-70</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1073,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9239</v>
+        <v>11499</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10758</v>
+        <v>11725</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1519</v>
+        <v>-226</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1108,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10277</v>
+        <v>13979</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10758</v>
+        <v>11725</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-481</v>
+        <v>2254</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1153,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1167,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12386</v>
+        <v>8258</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10758</v>
+        <v>7736</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1628</v>
+        <v>522</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1198,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1208,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11239</v>
+        <v>8046</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12754</v>
+        <v>7736</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1515</v>
+        <v>310</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1243,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1253,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11522</v>
+        <v>6947</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12754</v>
+        <v>7229</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1232</v>
+        <v>-282</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1288,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1298,33 +1316,5613 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>8046</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>7229</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>16-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>8046</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>6736</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1310</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>7863</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-1874</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-1028</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9103</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-634</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Nesma Airlines NE-120</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>12683</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>12754</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-71</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n">
+        <v>9709</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-2016</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-1494</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>10625</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>8046</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-3679</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-1494</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>23-JUN-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>7863</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-1874</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>23-JUN-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-1028</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>8046</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-1691</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1028</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>9009</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-1715</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-3467</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>9709</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-2016</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>10625</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>11217</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-508</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>11499</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-226</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>12359</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>634</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>8215</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-2509</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>8930</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1794</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>10203</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-521</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>9009</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1715</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>10625</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-99</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>10203</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>466</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>9709</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>9709</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>9009</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-2716</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>10569</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>10625</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>11499</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-226</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-1184</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>9709</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-1015</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-888</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>10724</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>10625</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>10625</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>11725</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>9709</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-9005</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-8878</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-8483</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>8930</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-9784</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>9709</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-9005</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-8878</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>12655</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-6059</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-8878</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>9836</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-8878</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>10569</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-8145</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>8930</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-9784</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>11217</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-7497</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>11753</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-6961</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>12655</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-6059</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>14191</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>14163</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-56</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>14191</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>14163</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-56</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>15727</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-2889</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>14191</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>15727</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-1536</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>14163</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>15727</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-1564</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>14191</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>15727</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-1536</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>20-AUG-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>14191</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>15727</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>-1536</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>14191</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>15727</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-1536</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>22-AUG-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>14191</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>15727</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-1536</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>14163</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-56</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>12838</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-1381</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>11217</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-7497</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>15050</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>15050</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04-SEP-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>15050</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>11217</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>-7497</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>15050</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>15050</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>15050</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>-3664</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-122</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>11217</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-7497</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>12232</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>-6482</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>8930</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>-9784</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>-9174</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>-9174</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>18714</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>-7525</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>11217</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>9737</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>1480</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10569</v>
+        <v>11753</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10724</v>
+        <v>9737</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-155</v>
+        <v>2016</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12655</v>
+        <v>12669</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>12725</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-70</v>
+        <v>-56</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1098,10 +1098,10 @@
         <v>11499</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11725</v>
+        <v>12725</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-226</v>
+        <v>-1226</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1143,10 +1143,10 @@
         <v>13979</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11725</v>
+        <v>12725</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2254</v>
+        <v>1254</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1188,10 +1188,10 @@
         <v>8258</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7736</v>
+        <v>9737</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>522</v>
+        <v>-1479</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8046</v>
+        <v>8272</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7736</v>
+        <v>9737</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>310</v>
+        <v>-1465</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6947</v>
+        <v>8723</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7229</v>
+        <v>9737</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-282</v>
+        <v>-1014</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1323,10 +1323,10 @@
         <v>8046</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7229</v>
+        <v>7736</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>817</v>
+        <v>310</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8046</v>
+        <v>7412</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>6736</v>
+        <v>7736</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1310</v>
+        <v>-324</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7863</v>
+        <v>8046</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9737</v>
+        <v>7229</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1874</v>
+        <v>817</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8709</v>
+        <v>6722</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9737</v>
+        <v>6736</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1028</v>
+        <v>-14</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9103</v>
+        <v>8046</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9737</v>
+        <v>6736</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-634</v>
+        <v>1310</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9709</v>
+        <v>7412</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11725</v>
+        <v>9737</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2016</v>
+        <v>-2325</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10231</v>
+        <v>7863</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11725</v>
+        <v>9737</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1494</v>
+        <v>-1874</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10625</v>
+        <v>9103</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11725</v>
+        <v>9737</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-1100</v>
+        <v>-634</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8046</v>
+        <v>9723</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-3679</v>
+        <v>-2016</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>10231</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1494</v>
+        <v>-1508</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7863</v>
+        <v>10625</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1874</v>
+        <v>-1114</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8709</v>
+        <v>8046</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-1028</v>
+        <v>-3693</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8046</v>
+        <v>10231</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1691</v>
+        <v>-1508</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>8709</v>
+        <v>7863</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1028</v>
+        <v>-1874</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8709</v>
+        <v>8723</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10724</v>
+        <v>9737</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-2015</v>
+        <v>-1014</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>9009</v>
+        <v>8046</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>10724</v>
+        <v>9737</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1715</v>
+        <v>-1691</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>10231</v>
+        <v>8723</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10724</v>
+        <v>9737</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-493</v>
+        <v>-1014</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8258</v>
+        <v>8723</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11725</v>
+        <v>10738</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-3467</v>
+        <v>-2015</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>9709</v>
+        <v>9012</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11725</v>
+        <v>10738</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-2016</v>
+        <v>-1726</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10625</v>
+        <v>10231</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11725</v>
+        <v>10738</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1100</v>
+        <v>-507</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>30</v>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11217</v>
+        <v>8258</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-508</v>
+        <v>-3481</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>11499</v>
+        <v>9723</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-226</v>
+        <v>-2016</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>30</v>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>12359</v>
+        <v>11189</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>634</v>
+        <v>-550</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>8215</v>
+        <v>11217</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>10724</v>
+        <v>11739</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-2509</v>
+        <v>-522</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>30</v>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>8930</v>
+        <v>11499</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>10724</v>
+        <v>11739</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1794</v>
+        <v>-240</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>10203</v>
+        <v>12359</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10724</v>
+        <v>11739</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-521</v>
+        <v>620</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2462,9 +2462,9 @@
       <c r="I44" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10231</v>
+        <v>8215</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-493</v>
+        <v>-2523</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>8709</v>
+        <v>8933</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-2015</v>
+        <v>-1805</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>9009</v>
+        <v>10203</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1715</v>
+        <v>-535</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
         <v>10231</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-493</v>
+        <v>-507</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>30</v>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10625</v>
+        <v>8723</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-99</v>
+        <v>-2015</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>30</v>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>10203</v>
+        <v>9012</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9737</v>
+        <v>10738</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>466</v>
+        <v>-1726</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>9709</v>
+        <v>10231</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>9737</v>
+        <v>10738</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-28</v>
+        <v>-507</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>30</v>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>9836</v>
+        <v>10203</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>99</v>
+        <v>466</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>9709</v>
+        <v>9723</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>30</v>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>9009</v>
+        <v>9723</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11725</v>
+        <v>9737</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-2716</v>
+        <v>-14</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,26 +2981,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>10569</v>
+        <v>9836</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>11725</v>
+        <v>9737</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1156</v>
+        <v>99</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>10625</v>
+        <v>10569</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1100</v>
+        <v>-1170</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>30</v>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11499</v>
+        <v>10625</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-226</v>
+        <v>-1114</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>30</v>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>9836</v>
+        <v>11499</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>99</v>
+        <v>-240</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>9540</v>
+        <v>9836</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10724</v>
+        <v>9737</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1184</v>
+        <v>99</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>9709</v>
+        <v>9540</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-1015</v>
+        <v>-1198</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>10231</v>
+        <v>9723</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-493</v>
+        <v>-1015</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>30</v>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>8709</v>
+        <v>10231</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-2015</v>
+        <v>-507</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>30</v>
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>9836</v>
+        <v>8723</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-888</v>
+        <v>-2015</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3386,26 +3386,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10231</v>
+        <v>8933</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10724</v>
+        <v>10738</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-493</v>
+        <v>-1805</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,30 +3431,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10625</v>
+        <v>9836</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11725</v>
+        <v>10738</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-1100</v>
+        <v>-902</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10625</v>
+        <v>10231</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11725</v>
+        <v>10738</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-1100</v>
+        <v>-507</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,26 +3521,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9836</v>
+        <v>9012</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>99</v>
+        <v>-2727</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9709</v>
+        <v>10625</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>18714</v>
+        <v>11739</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-9005</v>
+        <v>-1114</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3587,9 +3587,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,30 +3611,30 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9836</v>
+        <v>10625</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>18714</v>
+        <v>11739</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-8878</v>
+        <v>-1114</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10231</v>
+        <v>9836</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>18714</v>
+        <v>9737</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-8483</v>
+        <v>99</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,28 +3701,28 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>8930</v>
+        <v>9723</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-9784</v>
+        <v>-9006</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,28 +3746,28 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9709</v>
+        <v>9836</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-9005</v>
+        <v>-8893</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,28 +3791,28 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9836</v>
+        <v>10231</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-8878</v>
+        <v>-8498</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>11189</v>
+        <v>9723</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-7525</v>
+        <v>-9006</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>30</v>
@@ -3857,7 +3857,7 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,28 +3881,28 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>12655</v>
+        <v>9836</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-6059</v>
+        <v>-8893</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>12838</v>
+        <v>11189</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-5876</v>
+        <v>-7540</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>30</v>
@@ -3947,7 +3947,7 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3971,28 +3971,28 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>12838</v>
+        <v>9012</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-5876</v>
+        <v>-9717</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,28 +4016,28 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9836</v>
+        <v>12669</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-8878</v>
+        <v>-6060</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-5876</v>
+        <v>-5891</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>30</v>
@@ -4082,7 +4082,7 @@
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,28 +4106,28 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>9836</v>
+        <v>12838</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-8878</v>
+        <v>-5891</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,28 +4151,28 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>10569</v>
+        <v>9836</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-8145</v>
+        <v>-8893</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4203,10 +4203,10 @@
         <v>12838</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-5876</v>
+        <v>-5891</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>30</v>
@@ -4217,7 +4217,7 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,28 +4241,28 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>8930</v>
+        <v>9836</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-9784</v>
+        <v>-8893</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>11217</v>
+        <v>10569</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-7497</v>
+        <v>-8160</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>30</v>
@@ -4307,7 +4307,7 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="4" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,28 +4331,28 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>11753</v>
+        <v>12838</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-6961</v>
+        <v>-5891</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4376,28 +4376,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>12838</v>
+        <v>8933</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-5876</v>
+        <v>-9796</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>12655</v>
+        <v>11217</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-6059</v>
+        <v>-7512</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>30</v>
@@ -4442,7 +4442,7 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,28 +4466,28 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>12838</v>
+        <v>11753</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-5876</v>
+        <v>-6976</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-5876</v>
+        <v>-5891</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>30</v>
@@ -4532,7 +4532,7 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>14191</v>
+        <v>12669</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>14219</v>
+        <v>18729</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-28</v>
+        <v>-6060</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>30</v>
@@ -4577,9 +4577,9 @@
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14219</v>
+        <v>18729</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-1381</v>
+        <v>-5891</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>30</v>
@@ -4622,9 +4622,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>14163</v>
+        <v>12838</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>14219</v>
+        <v>18729</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-56</v>
+        <v>-5891</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>30</v>
@@ -4667,9 +4667,9 @@
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,26 +4691,26 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>12838</v>
+        <v>14916</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>14219</v>
+        <v>18729</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-1381</v>
+        <v>-3813</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-1381</v>
+        <v>-14</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>30</v>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-1381</v>
+        <v>-1395</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>30</v>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>14191</v>
+        <v>14163</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-28</v>
+        <v>-70</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>30</v>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4878,10 +4878,10 @@
         <v>12838</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-1381</v>
+        <v>-1395</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>30</v>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>14163</v>
+        <v>12838</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-56</v>
+        <v>-1395</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>30</v>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-1381</v>
+        <v>-1395</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>30</v>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-2889</v>
+        <v>-14</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>30</v>
@@ -5027,9 +5027,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>14191</v>
+        <v>12838</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-1536</v>
+        <v>-1395</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>30</v>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5103,10 +5103,10 @@
         <v>14163</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-1564</v>
+        <v>-70</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>30</v>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5145,13 +5145,13 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>14191</v>
+        <v>12838</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-1536</v>
+        <v>-1395</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>30</v>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14219</v>
+        <v>15727</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-1381</v>
+        <v>-2889</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>30</v>
@@ -5207,9 +5207,9 @@
       <c r="I105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>14191</v>
+        <v>14219</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>15727</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-1536</v>
+        <v>-1508</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>30</v>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>14191</v>
+        <v>14163</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>15727</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-1536</v>
+        <v>-1564</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>30</v>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>22-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>14191</v>
+        <v>14219</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>15727</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-1536</v>
+        <v>-1508</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>30</v>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14219</v>
+        <v>15727</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-1381</v>
+        <v>-1508</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>30</v>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>14163</v>
+        <v>14219</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14219</v>
+        <v>15727</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-56</v>
+        <v>-1508</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>30</v>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5460,13 +5460,13 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14219</v>
+        <v>15727</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-1381</v>
+        <v>-1508</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>30</v>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-1381</v>
+        <v>-1395</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>30</v>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>12838</v>
+        <v>14163</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-1381</v>
+        <v>-70</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>30</v>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>29-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5598,10 +5598,10 @@
         <v>12838</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>14219</v>
+        <v>14233</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-1381</v>
+        <v>-1395</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>30</v>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,17 +5636,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>11189</v>
+        <v>12838</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18714</v>
+        <v>14233</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-7525</v>
+        <v>-1395</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>30</v>
@@ -5657,9 +5657,9 @@
       <c r="I115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>11217</v>
+        <v>12838</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>18714</v>
+        <v>14233</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-7497</v>
+        <v>-1395</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>30</v>
@@ -5702,9 +5702,9 @@
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>29-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,30 +5726,30 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>15050</v>
+        <v>12838</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>18714</v>
+        <v>14233</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-3664</v>
+        <v>-1395</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5778,10 +5778,10 @@
         <v>11189</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-7525</v>
+        <v>-7540</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>30</v>
@@ -5792,7 +5792,7 @@
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,28 +5816,28 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>15050</v>
+        <v>11217</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-3664</v>
+        <v>-7512</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,28 +5861,28 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-7525</v>
+        <v>-3665</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
         <v>11189</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-7525</v>
+        <v>-7540</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>30</v>
@@ -5927,7 +5927,7 @@
       <c r="I121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="4" t="inlineStr">
+      <c r="J121" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,28 +5951,28 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-7525</v>
+        <v>-3665</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,28 +5996,28 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>15050</v>
+        <v>11189</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-3664</v>
+        <v>-7540</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
         <v>11189</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-7525</v>
+        <v>-7540</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>30</v>
@@ -6062,7 +6062,7 @@
       <c r="I124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="4" t="inlineStr">
+      <c r="J124" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-7497</v>
+        <v>-7540</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>30</v>
@@ -6107,7 +6107,7 @@
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="4" t="inlineStr">
+      <c r="J125" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>15050</v>
+        <v>15064</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-3664</v>
+        <v>-3665</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>46</v>
@@ -6152,7 +6152,7 @@
       <c r="I126" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J126" s="4" t="inlineStr">
+      <c r="J126" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6183,10 +6183,10 @@
         <v>11189</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-7525</v>
+        <v>-7540</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>30</v>
@@ -6197,7 +6197,7 @@
       <c r="I127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="4" t="inlineStr">
+      <c r="J127" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,28 +6221,28 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>15050</v>
+        <v>11217</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-3664</v>
+        <v>-7512</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,28 +6266,28 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-7525</v>
+        <v>-3665</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H129" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
         <v>11189</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-7525</v>
+        <v>-7540</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>30</v>
@@ -6332,7 +6332,7 @@
       <c r="I130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="4" t="inlineStr">
+      <c r="J130" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6356,28 +6356,28 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-7525</v>
+        <v>-3665</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,30 +6401,30 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>15050</v>
+        <v>16419</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-3664</v>
+        <v>-2310</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,17 +6446,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
         <v>11189</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-7525</v>
+        <v>-7540</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>30</v>
@@ -6467,7 +6467,7 @@
       <c r="I133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J133" s="4" t="inlineStr">
+      <c r="J133" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-7497</v>
+        <v>-7540</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>30</v>
@@ -6512,7 +6512,7 @@
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="4" t="inlineStr">
+      <c r="J134" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,30 +6536,30 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>12232</v>
+        <v>16498</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-6482</v>
+        <v>-2231</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,28 +6581,28 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>8930</v>
+        <v>11189</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-9784</v>
+        <v>-7540</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6616,7 +6616,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6630,24 +6630,24 @@
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>9540</v>
+        <v>15064</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-9174</v>
+        <v>-3665</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6678,10 +6678,10 @@
         <v>11189</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-7525</v>
+        <v>-7540</v>
       </c>
       <c r="G138" s="2" t="n">
         <v>30</v>
@@ -6692,7 +6692,7 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="4" t="inlineStr">
+      <c r="J138" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>11189</v>
+        <v>11217</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-7525</v>
+        <v>-7512</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>30</v>
@@ -6737,7 +6737,7 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="4" t="inlineStr">
+      <c r="J139" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,30 +6761,30 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>11189</v>
+        <v>12246</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-7525</v>
+        <v>-6483</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H140" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,28 +6806,28 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>9540</v>
+        <v>8933</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-9174</v>
+        <v>-9796</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,28 +6851,28 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>11189</v>
+        <v>9540</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>18714</v>
+        <v>18729</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-7525</v>
+        <v>-9189</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6886,43 +6886,313 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>-7540</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>9012</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>-9717</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-307</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>-7540</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-107</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>-7540</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>-9189</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>-7540</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-811</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n">
+      <c r="D149" s="2" t="n">
         <v>11217</v>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E149" s="2" t="n">
         <v>9737</v>
       </c>
-      <c r="F143" s="2" t="n">
+      <c r="F149" s="2" t="n">
         <v>1480</v>
       </c>
-      <c r="G143" s="2" t="n">
+      <c r="G149" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H143" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I143" s="2" t="n">
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11753</v>
+        <v>11189</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9737</v>
+        <v>12725</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2016</v>
+        <v>-1536</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11189</v>
+        <v>12669</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>12725</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1536</v>
+        <v>-56</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12669</v>
+        <v>11499</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>12725</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-56</v>
+        <v>-1226</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11499</v>
+        <v>13979</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>12725</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1226</v>
+        <v>1254</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>13979</v>
+        <v>8258</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12725</v>
+        <v>9737</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1254</v>
+        <v>-1479</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8258</v>
+        <v>8272</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1479</v>
+        <v>-1465</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8272</v>
+        <v>8723</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1465</v>
+        <v>-1014</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8723</v>
+        <v>8046</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9737</v>
+        <v>7736</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1014</v>
+        <v>310</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8046</v>
+        <v>7412</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>7736</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>310</v>
+        <v>-324</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7412</v>
+        <v>8046</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7736</v>
+        <v>7229</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-324</v>
+        <v>817</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8046</v>
+        <v>6722</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7229</v>
+        <v>6736</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>817</v>
+        <v>-14</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6722</v>
+        <v>8046</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>6736</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-14</v>
+        <v>1310</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8046</v>
+        <v>7412</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6736</v>
+        <v>9737</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1310</v>
+        <v>-2325</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7412</v>
+        <v>7863</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2325</v>
+        <v>-1874</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7863</v>
+        <v>9103</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1874</v>
+        <v>-634</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9103</v>
+        <v>9723</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-634</v>
+        <v>-2016</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9723</v>
+        <v>10231</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-2016</v>
+        <v>-1508</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10231</v>
+        <v>10625</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1508</v>
+        <v>-1114</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>10625</v>
+        <v>8046</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1114</v>
+        <v>-3693</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8046</v>
+        <v>10231</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-3693</v>
+        <v>-1508</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,26 +1856,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>10231</v>
+        <v>7863</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11739</v>
+        <v>9737</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1508</v>
+        <v>-1874</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7863</v>
+        <v>8723</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1874</v>
+        <v>-1014</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8723</v>
+        <v>8046</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1014</v>
+        <v>-1691</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8046</v>
+        <v>8723</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1691</v>
+        <v>-1014</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
         <v>8723</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>9737</v>
+        <v>10738</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1014</v>
+        <v>-2015</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8723</v>
+        <v>9012</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-2015</v>
+        <v>-1726</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>9012</v>
+        <v>10231</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1726</v>
+        <v>-507</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10231</v>
+        <v>8258</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>10738</v>
+        <v>11739</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-507</v>
+        <v>-3481</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8258</v>
+        <v>9723</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-3481</v>
+        <v>-2016</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9723</v>
+        <v>11189</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-2016</v>
+        <v>-550</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>30</v>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>11189</v>
+        <v>11217</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-550</v>
+        <v>-522</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>30</v>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>11217</v>
+        <v>11499</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-522</v>
+        <v>-240</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>30</v>
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>11499</v>
+        <v>12359</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-240</v>
+        <v>620</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>12359</v>
+        <v>8215</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11739</v>
+        <v>10738</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>620</v>
+        <v>-2523</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>8215</v>
+        <v>8933</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-2523</v>
+        <v>-1805</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>8933</v>
+        <v>10203</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1805</v>
+        <v>-535</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10203</v>
+        <v>10231</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-535</v>
+        <v>-507</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10231</v>
+        <v>8723</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-507</v>
+        <v>-2015</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>30</v>
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>8723</v>
+        <v>9012</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-2015</v>
+        <v>-1726</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>9012</v>
+        <v>10231</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1726</v>
+        <v>-507</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>10231</v>
+        <v>10203</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>10738</v>
+        <v>9737</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-507</v>
+        <v>466</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10203</v>
+        <v>9723</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>466</v>
+        <v>-14</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>9723</v>
+        <v>9836</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-14</v>
+        <v>99</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,26 +2891,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>9836</v>
+        <v>9723</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>99</v>
+        <v>-14</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>9723</v>
+        <v>9836</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-14</v>
+        <v>99</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,26 +2981,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>9836</v>
+        <v>9012</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>99</v>
+        <v>-2727</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3836,26 +3836,26 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9723</v>
+        <v>8933</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-9006</v>
+        <v>-9796</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
@@ -3881,26 +3881,26 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9836</v>
+        <v>9723</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-8893</v>
+        <v>-9006</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
@@ -3926,26 +3926,26 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>11189</v>
+        <v>9836</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-7540</v>
+        <v>-8893</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,26 +3971,26 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>9012</v>
+        <v>11189</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-9717</v>
+        <v>-7540</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
@@ -4016,26 +4016,26 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>12669</v>
+        <v>9012</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-6060</v>
+        <v>-9717</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>12838</v>
+        <v>12669</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-5891</v>
+        <v>-6060</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>30</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,26 +4151,26 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>9836</v>
+        <v>12838</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-8893</v>
+        <v>-5891</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
@@ -4196,26 +4196,26 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>12838</v>
+        <v>9836</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-5891</v>
+        <v>-8893</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,26 +4241,26 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9836</v>
+        <v>12838</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-8893</v>
+        <v>-5891</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
@@ -4286,26 +4286,26 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>10569</v>
+        <v>9836</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-8160</v>
+        <v>-8893</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>12838</v>
+        <v>10569</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-5891</v>
+        <v>-8160</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>30</v>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,26 +4376,26 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>8933</v>
+        <v>12838</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-9796</v>
+        <v>-5891</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
@@ -4421,26 +4421,26 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>11217</v>
+        <v>8933</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-7512</v>
+        <v>-9796</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
@@ -4466,26 +4466,26 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>11753</v>
+        <v>11217</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-6976</v>
+        <v>-7512</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
@@ -4511,26 +4511,26 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>12838</v>
+        <v>11753</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-5891</v>
+        <v>-6976</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>12669</v>
+        <v>12838</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-6060</v>
+        <v>-5891</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>30</v>
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12838</v>
+        <v>12669</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-5891</v>
+        <v>-6060</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>30</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
@@ -4691,30 +4691,30 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>14916</v>
+        <v>12838</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-3813</v>
+        <v>-5891</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,26 +4736,26 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>14219</v>
+        <v>14916</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>14233</v>
+        <v>18729</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-14</v>
+        <v>-3813</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4785,13 +4785,13 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-1395</v>
+        <v>-14</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>30</v>
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>14163</v>
+        <v>12838</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-70</v>
+        <v>-1395</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>30</v>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>12838</v>
+        <v>14163</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-1395</v>
+        <v>-70</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>30</v>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>14219</v>
+        <v>12838</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-14</v>
+        <v>-1395</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>30</v>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-1395</v>
+        <v>-14</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>30</v>
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>14163</v>
+        <v>12838</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-70</v>
+        <v>-1395</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>30</v>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>12838</v>
+        <v>14163</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-1395</v>
+        <v>-70</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>30</v>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-2889</v>
+        <v>-1395</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>30</v>
@@ -5207,9 +5207,9 @@
       <c r="I105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>14219</v>
+        <v>12838</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>15727</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-1508</v>
+        <v>-2889</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>30</v>
@@ -5252,9 +5252,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>14163</v>
+        <v>14219</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>15727</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-1564</v>
+        <v>-1508</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>30</v>
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>14219</v>
+        <v>14163</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>15727</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-1508</v>
+        <v>-1564</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>30</v>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>22-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5505,13 +5505,13 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14233</v>
+        <v>15727</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-1395</v>
+        <v>-1508</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>30</v>
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>14163</v>
+        <v>12838</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-70</v>
+        <v>-1395</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>30</v>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>12838</v>
+        <v>14163</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-1395</v>
+        <v>-70</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>30</v>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>29-AUG-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>29-AUG-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5775,13 +5775,13 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>11189</v>
+        <v>12838</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>18729</v>
+        <v>14233</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-7540</v>
+        <v>-1395</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>30</v>
@@ -5792,9 +5792,9 @@
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-7512</v>
+        <v>-7540</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>30</v>
@@ -5861,26 +5861,26 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>15064</v>
+        <v>11217</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-3665</v>
+        <v>-7512</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,26 +5906,26 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-7540</v>
+        <v>-3665</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
@@ -5951,26 +5951,26 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,26 +5996,26 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-7540</v>
+        <v>-3665</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
@@ -6131,26 +6131,26 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,26 +6176,26 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-7540</v>
+        <v>-3665</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
@@ -6221,17 +6221,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-7512</v>
+        <v>-7540</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>30</v>
@@ -6266,26 +6266,26 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>15064</v>
+        <v>11217</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-3665</v>
+        <v>-7512</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H129" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,26 +6311,26 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-7540</v>
+        <v>-3665</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
@@ -6356,26 +6356,26 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
@@ -6401,30 +6401,30 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>16419</v>
+        <v>15064</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-2310</v>
+        <v>-3665</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,30 +6446,30 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>11189</v>
+        <v>16419</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-7540</v>
+        <v>-2310</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H133" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
@@ -6536,30 +6536,30 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>16498</v>
+        <v>11189</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-2231</v>
+        <v>-7540</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,30 +6581,30 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>11189</v>
+        <v>16498</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-7540</v>
+        <v>-2231</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6626,26 +6626,26 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6671,26 +6671,26 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-7540</v>
+        <v>-3665</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
@@ -6716,17 +6716,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-7512</v>
+        <v>-7540</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>30</v>
@@ -6761,30 +6761,30 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>12246</v>
+        <v>11217</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-6483</v>
+        <v>-7512</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H140" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,30 +6806,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>8933</v>
+        <v>12246</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-9796</v>
+        <v>-6483</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J141" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6851,26 +6851,26 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>9540</v>
+        <v>8933</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-9189</v>
+        <v>-9796</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
@@ -6896,26 +6896,26 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>11189</v>
+        <v>9540</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-7540</v>
+        <v>-9189</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6941,26 +6941,26 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>9012</v>
+        <v>11189</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-9717</v>
+        <v>-7540</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
@@ -6986,26 +6986,26 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>11189</v>
+        <v>9012</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-7540</v>
+        <v>-9717</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H145" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
@@ -7066,7 +7066,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7076,26 +7076,26 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>9540</v>
+        <v>11189</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>-9189</v>
+        <v>-7540</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
@@ -7121,26 +7121,26 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>11189</v>
+        <v>9540</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>-7540</v>
+        <v>-9189</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H148" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
@@ -7156,43 +7156,88 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-207</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>11189</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>18729</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>-7540</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-325</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-811</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D150" s="2" t="n">
         <v>11217</v>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E150" s="2" t="n">
         <v>9737</v>
       </c>
-      <c r="F149" s="2" t="n">
+      <c r="F150" s="2" t="n">
         <v>1480</v>
       </c>
-      <c r="G149" s="2" t="n">
+      <c r="G150" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H149" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I149" s="2" t="n">
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>9012</v>
+        <v>9008</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1726</v>
+        <v>-1730</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>20</v>
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>8933</v>
+        <v>10203</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1805</v>
+        <v>-535</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10203</v>
+        <v>10231</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-535</v>
+        <v>-507</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10231</v>
+        <v>8723</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-507</v>
+        <v>-2015</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>30</v>
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>8723</v>
+        <v>9008</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-2015</v>
+        <v>-1730</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>9012</v>
+        <v>10231</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1726</v>
+        <v>-507</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>10231</v>
+        <v>10203</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>10738</v>
+        <v>9737</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-507</v>
+        <v>466</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>10203</v>
+        <v>9723</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>466</v>
+        <v>-14</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>9723</v>
+        <v>9836</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-14</v>
+        <v>99</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>9836</v>
+        <v>9723</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>99</v>
+        <v>-14</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2891,26 +2891,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>9723</v>
+        <v>9836</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>9737</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-14</v>
+        <v>99</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>9836</v>
+        <v>10569</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>9737</v>
+        <v>11739</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>99</v>
+        <v>-1170</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2981,26 +2981,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>9012</v>
+        <v>10625</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-2727</v>
+        <v>-1114</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>10569</v>
+        <v>11499</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1170</v>
+        <v>-240</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>30</v>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>10625</v>
+        <v>9836</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>11739</v>
+        <v>9737</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-1114</v>
+        <v>99</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11499</v>
+        <v>9540</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>11739</v>
+        <v>10738</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-240</v>
+        <v>-1198</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>9836</v>
+        <v>9723</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>9737</v>
+        <v>10738</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>99</v>
+        <v>-1015</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>9540</v>
+        <v>10231</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-1198</v>
+        <v>-507</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>9723</v>
+        <v>8723</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-1015</v>
+        <v>-2015</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>30</v>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,26 +3296,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>10231</v>
+        <v>8929</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-507</v>
+        <v>-1809</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>8723</v>
+        <v>9836</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-2015</v>
+        <v>-902</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3386,26 +3386,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>8933</v>
+        <v>10231</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>10738</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-1805</v>
+        <v>-507</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,30 +3431,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>9836</v>
+        <v>9008</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10738</v>
+        <v>11739</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-902</v>
+        <v>-2731</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10231</v>
+        <v>10625</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>10738</v>
+        <v>11739</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-507</v>
+        <v>-1114</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3521,26 +3521,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9012</v>
+        <v>10625</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>11739</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-2727</v>
+        <v>-1114</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,26 +3566,26 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>10625</v>
+        <v>9836</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>11739</v>
+        <v>9737</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-1114</v>
+        <v>99</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10625</v>
+        <v>9723</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>11739</v>
+        <v>18729</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-1114</v>
+        <v>-9006</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3632,9 +3632,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3663,10 +3663,10 @@
         <v>9836</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>9737</v>
+        <v>18729</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>99</v>
+        <v>-8893</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>46</v>
@@ -3677,9 +3677,9 @@
       <c r="I71" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9723</v>
+        <v>10231</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-9006</v>
+        <v>-8498</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,26 +3746,26 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9836</v>
+        <v>9723</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-8893</v>
+        <v>-9006</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,26 +3791,26 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>10231</v>
+        <v>9836</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-8498</v>
+        <v>-8893</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
@@ -3836,26 +3836,26 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>8933</v>
+        <v>11189</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-9796</v>
+        <v>-7540</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,26 +3881,26 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9723</v>
+        <v>9008</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-9006</v>
+        <v>-9721</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,26 +3926,26 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9836</v>
+        <v>12669</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-8893</v>
+        <v>-6060</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>11189</v>
+        <v>12838</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-7540</v>
+        <v>-5891</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>30</v>
@@ -4016,26 +4016,26 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9012</v>
+        <v>12838</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-9717</v>
+        <v>-5891</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,26 +4061,26 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>12669</v>
+        <v>9836</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-6060</v>
+        <v>-8893</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,26 +4151,26 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>12838</v>
+        <v>9836</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-5891</v>
+        <v>-8893</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,26 +4196,26 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>9836</v>
+        <v>10569</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-8893</v>
+        <v>-8160</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,26 +4286,26 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>9836</v>
+        <v>11217</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-8893</v>
+        <v>-7512</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,26 +4331,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>10569</v>
+        <v>11753</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-8160</v>
+        <v>-6976</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,26 +4421,26 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>8933</v>
+        <v>12669</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-9796</v>
+        <v>-6060</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>11217</v>
+        <v>12838</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-7512</v>
+        <v>-5891</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>30</v>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,26 +4511,26 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>11753</v>
+        <v>12838</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-6976</v>
+        <v>-5891</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>18729</v>
+        <v>14233</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-5891</v>
+        <v>-14</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>30</v>
@@ -4577,9 +4577,9 @@
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12669</v>
+        <v>12838</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>18729</v>
+        <v>14233</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-6060</v>
+        <v>-1395</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>30</v>
@@ -4622,9 +4622,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>12838</v>
+        <v>14163</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>18729</v>
+        <v>14233</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-5891</v>
+        <v>-70</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>30</v>
@@ -4667,9 +4667,9 @@
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
         <v>12838</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>18729</v>
+        <v>14233</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-5891</v>
+        <v>-1395</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>30</v>
@@ -4712,9 +4712,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,26 +4736,26 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>14916</v>
+        <v>12838</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>18729</v>
+        <v>14233</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-3813</v>
+        <v>-1395</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>14219</v>
+        <v>12838</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-14</v>
+        <v>-1395</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>30</v>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4830,13 +4830,13 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-1395</v>
+        <v>-14</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>30</v>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>14163</v>
+        <v>12838</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-70</v>
+        <v>-1395</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>30</v>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>12838</v>
+        <v>14163</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>14233</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-1395</v>
+        <v>-70</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>30</v>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5013,10 +5013,10 @@
         <v>12838</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>14233</v>
+        <v>15727</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-1395</v>
+        <v>-2889</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>30</v>
@@ -5027,9 +5027,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
         <v>14219</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>14233</v>
+        <v>15727</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-14</v>
+        <v>-1508</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>30</v>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>12838</v>
+        <v>14163</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>14233</v>
+        <v>15727</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-1395</v>
+        <v>-1564</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>30</v>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>14163</v>
+        <v>14219</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>14233</v>
+        <v>15727</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-70</v>
+        <v>-1508</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>30</v>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14233</v>
+        <v>15727</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-1395</v>
+        <v>-1508</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>30</v>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>12838</v>
+        <v>14219</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>15727</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-2889</v>
+        <v>-1508</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>30</v>
@@ -5252,9 +5252,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>14163</v>
+        <v>12838</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-1564</v>
+        <v>-1395</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>30</v>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>14219</v>
+        <v>14163</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-1508</v>
+        <v>-70</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>30</v>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>14219</v>
+        <v>12838</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-1508</v>
+        <v>-1395</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>30</v>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>14219</v>
+        <v>12838</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-1508</v>
+        <v>-1395</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>30</v>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>22-AUG-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>14219</v>
+        <v>12838</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>15727</v>
+        <v>14233</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-1508</v>
+        <v>-1395</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>30</v>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>29-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>14163</v>
+        <v>11189</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>14233</v>
+        <v>18729</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-70</v>
+        <v>-7540</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>30</v>
@@ -5612,9 +5612,9 @@
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,17 +5636,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>12838</v>
+        <v>11217</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>14233</v>
+        <v>18729</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-1395</v>
+        <v>-7512</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>30</v>
@@ -5657,9 +5657,9 @@
       <c r="I115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,30 +5681,30 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>12838</v>
+        <v>15064</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14233</v>
+        <v>18729</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-1395</v>
+        <v>-3665</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>12838</v>
+        <v>11189</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14233</v>
+        <v>18729</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-1395</v>
+        <v>-7540</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>30</v>
@@ -5747,9 +5747,9 @@
       <c r="I117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,30 +5771,30 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>12838</v>
+        <v>15064</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>14233</v>
+        <v>18729</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-1395</v>
+        <v>-3665</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-7512</v>
+        <v>-7540</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>30</v>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,26 +5906,26 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,26 +5951,26 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-7540</v>
+        <v>-3665</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,26 +5996,26 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>11189</v>
+        <v>11217</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-7540</v>
+        <v>-7512</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>30</v>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,26 +6086,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>11189</v>
+        <v>15064</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-7540</v>
+        <v>-3665</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,30 +6221,30 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>11189</v>
+        <v>16411</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-7540</v>
+        <v>-2318</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-7512</v>
+        <v>-7540</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>30</v>
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,26 +6311,26 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6356,30 +6356,30 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>11189</v>
+        <v>16490</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-7540</v>
+        <v>-2239</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,26 +6401,26 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,30 +6446,30 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>16419</v>
+        <v>15064</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-2310</v>
+        <v>-3665</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>11189</v>
+        <v>11217</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-7540</v>
+        <v>-7512</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>30</v>
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,30 +6581,30 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>16498</v>
+        <v>12246</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-2231</v>
+        <v>-6483</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6626,26 +6626,26 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>11189</v>
+        <v>9540</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-7540</v>
+        <v>-9189</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6671,26 +6671,26 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>15064</v>
+        <v>11189</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-3665</v>
+        <v>-7540</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,26 +6716,26 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>11189</v>
+        <v>9008</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-7540</v>
+        <v>-9721</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,17 +6761,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>11217</v>
+        <v>11189</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-7512</v>
+        <v>-7540</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>30</v>
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,30 +6806,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>12246</v>
+        <v>11189</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-6483</v>
+        <v>-7540</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,26 +6851,26 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>8933</v>
+        <v>9540</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-9796</v>
+        <v>-9189</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6896,26 +6896,26 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>9540</v>
+        <v>11189</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>18729</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-9189</v>
+        <v>-7540</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6941,303 +6941,33 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>11189</v>
+        <v>11217</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>18729</v>
+        <v>9737</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-7540</v>
+        <v>1480</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-599</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>9012</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>18729</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>-9717</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J145" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>11189</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>18729</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>-7540</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>11189</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>18729</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>-7540</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>9540</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>18729</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>-9189</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="n">
-        <v>11189</v>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>18729</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>-7540</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="n">
-        <v>11217</v>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>9737</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>1480</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4918</v>
+        <v>9689</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4960</v>
+        <v>9703</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-42</v>
+        <v>-14</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,27 +586,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4918</v>
+        <v>10177</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4960</v>
+        <v>10708</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-42</v>
+        <v>-531</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-979</t>
+          <t>SM-325</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4946</v>
+        <v>10177</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4960</v>
+        <v>10708</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-14</v>
+        <v>-531</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4918</v>
+        <v>10540</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4960</v>
+        <v>10708</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-42</v>
+        <v>-168</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4918</v>
+        <v>11434</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4960</v>
+        <v>11713</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-42</v>
+        <v>-279</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-117</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4918</v>
+        <v>6687</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4960</v>
+        <v>7692</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-42</v>
+        <v>-1005</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4946</v>
+        <v>6924</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4960</v>
+        <v>7692</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-14</v>
+        <v>-768</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6087</v>
+        <v>8488</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6243</v>
+        <v>7692</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-156</v>
+        <v>796</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6947</v>
+        <v>6924</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7229</v>
+        <v>7692</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-282</v>
+        <v>-768</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11189</v>
+        <v>8209</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12725</v>
+        <v>7692</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1536</v>
+        <v>517</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12669</v>
+        <v>6687</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12725</v>
+        <v>7692</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-56</v>
+        <v>-1005</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11499</v>
+        <v>6924</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12725</v>
+        <v>7692</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1226</v>
+        <v>-768</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13979</v>
+        <v>6924</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12725</v>
+        <v>7692</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1254</v>
+        <v>-768</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8258</v>
+        <v>6687</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9737</v>
+        <v>7204</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1479</v>
+        <v>-517</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8272</v>
+        <v>6924</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9737</v>
+        <v>7204</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1465</v>
+        <v>-280</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8723</v>
+        <v>8209</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9737</v>
+        <v>7204</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1014</v>
+        <v>1005</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8046</v>
+        <v>6687</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7736</v>
+        <v>6701</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>310</v>
+        <v>-14</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7412</v>
+        <v>7985</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7736</v>
+        <v>6701</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-324</v>
+        <v>1284</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8046</v>
+        <v>7385</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7229</v>
+        <v>9703</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>817</v>
+        <v>-2318</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6722</v>
+        <v>7985</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6736</v>
+        <v>9703</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-14</v>
+        <v>-1718</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8046</v>
+        <v>8209</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6736</v>
+        <v>9703</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1310</v>
+        <v>-1494</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7412</v>
+        <v>8181</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9737</v>
+        <v>11713</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2325</v>
+        <v>-3532</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7863</v>
+        <v>8209</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9737</v>
+        <v>11713</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1874</v>
+        <v>-3504</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9103</v>
+        <v>8209</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>9737</v>
+        <v>11713</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-634</v>
+        <v>-3504</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1607,9 +1607,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9723</v>
+        <v>7985</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-2016</v>
+        <v>-3728</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>10231</v>
+        <v>9033</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-1508</v>
+        <v>-2680</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10625</v>
+        <v>7385</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11739</v>
+        <v>9703</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1114</v>
+        <v>-2318</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1770,26 +1770,26 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>8046</v>
+        <v>7804</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11739</v>
+        <v>9703</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-3693</v>
+        <v>-1899</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>10231</v>
+        <v>8209</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11739</v>
+        <v>9703</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-1508</v>
+        <v>-1494</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,26 +1856,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7863</v>
+        <v>7385</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1874</v>
+        <v>-2318</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>8723</v>
+        <v>7985</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1014</v>
+        <v>-1718</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8046</v>
+        <v>8209</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1691</v>
+        <v>-1494</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8723</v>
+        <v>8181</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9737</v>
+        <v>10708</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1014</v>
+        <v>-2527</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>8723</v>
+        <v>8209</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-2015</v>
+        <v>-2499</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>9008</v>
+        <v>8209</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1730</v>
+        <v>-2499</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10231</v>
+        <v>8181</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>10738</v>
+        <v>11713</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-507</v>
+        <v>-3532</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>30</v>
@@ -2147,9 +2147,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8258</v>
+        <v>8209</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-3481</v>
+        <v>-3504</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>9723</v>
+        <v>8488</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-2016</v>
+        <v>-3225</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>11189</v>
+        <v>11197</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11739</v>
+        <v>12704</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-550</v>
+        <v>-1507</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>30</v>
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>11217</v>
+        <v>11434</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11739</v>
+        <v>12704</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-522</v>
+        <v>-1270</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>30</v>
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>11499</v>
+        <v>12816</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11739</v>
+        <v>12704</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-240</v>
+        <v>112</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>12359</v>
+        <v>8684</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11739</v>
+        <v>10708</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>620</v>
+        <v>-2024</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>8215</v>
+        <v>8857</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-2523</v>
+        <v>-1851</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10203</v>
+        <v>10177</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-535</v>
+        <v>-531</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10231</v>
+        <v>10652</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-507</v>
+        <v>-56</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>8723</v>
+        <v>8684</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-2015</v>
+        <v>-2024</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>30</v>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>9008</v>
+        <v>8935</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1730</v>
+        <v>-1773</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>20</v>
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10231</v>
+        <v>10177</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-507</v>
+        <v>-531</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>30</v>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>10203</v>
+        <v>11127</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>466</v>
+        <v>1424</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>9723</v>
+        <v>9689</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>-14</v>
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>9836</v>
+        <v>10289</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>99</v>
+        <v>586</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>9723</v>
+        <v>9689</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>-14</v>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>9836</v>
+        <v>10289</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>99</v>
+        <v>586</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>10569</v>
+        <v>8927</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-1170</v>
+        <v>-2786</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>10625</v>
+        <v>9689</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1114</v>
+        <v>-2024</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>30</v>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11499</v>
+        <v>10568</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-240</v>
+        <v>-1145</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>30</v>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>9836</v>
+        <v>11434</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>9737</v>
+        <v>11713</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>99</v>
+        <v>-279</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>9540</v>
+        <v>10289</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10738</v>
+        <v>9703</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-1198</v>
+        <v>586</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>9723</v>
+        <v>9689</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1015</v>
+        <v>-1019</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>30</v>
@@ -3210,13 +3210,13 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10231</v>
+        <v>10177</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-507</v>
+        <v>-531</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>30</v>
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>8723</v>
+        <v>8684</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-2015</v>
+        <v>-2024</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>30</v>
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>8929</v>
+        <v>8857</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-1809</v>
+        <v>-1851</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>20</v>
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>9836</v>
+        <v>10177</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-902</v>
+        <v>-531</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10231</v>
+        <v>10289</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10738</v>
+        <v>10708</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-507</v>
+        <v>-419</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3431,26 +3431,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>9008</v>
+        <v>10568</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-2731</v>
+        <v>-1145</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10625</v>
+        <v>10568</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11739</v>
+        <v>11713</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-1114</v>
+        <v>-1145</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,26 +3521,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>10625</v>
+        <v>10289</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>11739</v>
+        <v>9703</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-1114</v>
+        <v>586</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9836</v>
+        <v>9689</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>9737</v>
+        <v>18722</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>99</v>
+        <v>-9033</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9723</v>
+        <v>10177</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-9006</v>
+        <v>-8545</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9836</v>
+        <v>10289</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-8893</v>
+        <v>-8433</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>46</v>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>10231</v>
+        <v>9689</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-8498</v>
+        <v>-9033</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3746,26 +3746,26 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9723</v>
+        <v>10289</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-9006</v>
+        <v>-8433</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
@@ -3791,26 +3791,26 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9836</v>
+        <v>11155</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-8893</v>
+        <v>-7567</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,26 +3836,26 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>11189</v>
+        <v>8935</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-7540</v>
+        <v>-9787</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
@@ -3881,26 +3881,26 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9008</v>
+        <v>12649</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-9721</v>
+        <v>-6073</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
@@ -3926,17 +3926,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>12669</v>
+        <v>12788</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-6060</v>
+        <v>-5934</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>30</v>
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-5891</v>
+        <v>-5934</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>30</v>
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,26 +4016,26 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>12838</v>
+        <v>10289</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-5891</v>
+        <v>-8433</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
@@ -4061,26 +4061,26 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9836</v>
+        <v>12788</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-8893</v>
+        <v>-5934</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,17 +4106,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>12838</v>
+        <v>10540</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-5891</v>
+        <v>-8182</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>30</v>
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>9836</v>
+        <v>10652</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-8893</v>
+        <v>-8070</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>46</v>
@@ -4196,17 +4196,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>10569</v>
+        <v>12788</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-8160</v>
+        <v>-5934</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>30</v>
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,26 +4241,26 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>12838</v>
+        <v>8857</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-5891</v>
+        <v>-9865</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>11217</v>
+        <v>11197</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-7512</v>
+        <v>-7525</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>30</v>
@@ -4335,13 +4335,13 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>11753</v>
+        <v>12216</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-6976</v>
+        <v>-6506</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>46</v>
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-5891</v>
+        <v>-5934</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>30</v>
@@ -4425,13 +4425,13 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>12669</v>
+        <v>12649</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-6060</v>
+        <v>-6073</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>30</v>
@@ -4470,13 +4470,13 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-5891</v>
+        <v>-5934</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>30</v>
@@ -4515,13 +4515,13 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-5891</v>
+        <v>-5934</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>30</v>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,26 +4556,26 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>14219</v>
+        <v>14789</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>14233</v>
+        <v>18722</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-14</v>
+        <v>-3933</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-1395</v>
+        <v>-1424</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>30</v>
@@ -4646,17 +4646,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>14163</v>
+        <v>12788</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-70</v>
+        <v>-1424</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>30</v>
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>12838</v>
+        <v>14143</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-1395</v>
+        <v>-69</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>30</v>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-1395</v>
+        <v>-1424</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>30</v>
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-1395</v>
+        <v>-1424</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>30</v>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>14219</v>
+        <v>12788</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-14</v>
+        <v>-1424</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>30</v>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4875,13 +4875,13 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>12838</v>
+        <v>14156</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-1395</v>
+        <v>-56</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>30</v>
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>14163</v>
+        <v>12788</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-70</v>
+        <v>-1424</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>30</v>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>12838</v>
+        <v>14143</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-1395</v>
+        <v>-69</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>30</v>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>15727</v>
+        <v>14212</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-2889</v>
+        <v>-1424</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>30</v>
@@ -5027,9 +5027,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>14219</v>
+        <v>12788</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15727</v>
+        <v>15720</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-1508</v>
+        <v>-2932</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>30</v>
@@ -5072,9 +5072,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,14 +5096,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>14163</v>
+        <v>14156</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15727</v>
+        <v>15720</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>-1564</v>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5145,13 +5145,13 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>14219</v>
+        <v>14156</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>15727</v>
+        <v>15720</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-1508</v>
+        <v>-1564</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>30</v>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>14219</v>
+        <v>14143</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>15727</v>
+        <v>15720</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-1508</v>
+        <v>-1577</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>30</v>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>14219</v>
+        <v>14156</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15727</v>
+        <v>15720</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-1508</v>
+        <v>-1564</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>30</v>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>22-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>14219</v>
+        <v>14156</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>15727</v>
+        <v>15720</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-1508</v>
+        <v>-1564</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>30</v>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>12838</v>
+        <v>14156</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>14233</v>
+        <v>15720</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-1395</v>
+        <v>-1564</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>30</v>
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>14163</v>
+        <v>12788</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-70</v>
+        <v>-1424</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>30</v>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>12838</v>
+        <v>14143</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-1395</v>
+        <v>-69</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>30</v>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-1395</v>
+        <v>-1424</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>30</v>
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>12838</v>
+        <v>12788</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-1395</v>
+        <v>-1424</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>30</v>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>29-AUG-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>12838</v>
+        <v>14156</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-1395</v>
+        <v>-56</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>30</v>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>29-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5595,13 +5595,13 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>11189</v>
+        <v>12788</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>18729</v>
+        <v>14212</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-7540</v>
+        <v>-1424</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>30</v>
@@ -5612,9 +5612,9 @@
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5636,17 +5636,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>11217</v>
+        <v>11155</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-7512</v>
+        <v>-7567</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>30</v>
@@ -5681,26 +5681,26 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>15064</v>
+        <v>11197</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-3665</v>
+        <v>-7525</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,26 +5726,26 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>11189</v>
+        <v>15525</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-7540</v>
+        <v>-3197</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
@@ -5771,26 +5771,26 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>15064</v>
+        <v>11155</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-3665</v>
+        <v>-7567</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,26 +5816,26 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>11189</v>
+        <v>15525</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-7540</v>
+        <v>-3197</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>30</v>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>30</v>
@@ -5951,26 +5951,26 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>15064</v>
+        <v>11155</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-3665</v>
+        <v>-7567</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,26 +5996,26 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>11189</v>
+        <v>15525</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-7540</v>
+        <v>-3197</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>11217</v>
+        <v>11155</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-7512</v>
+        <v>-7567</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>30</v>
@@ -6086,26 +6086,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>15064</v>
+        <v>11197</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-3665</v>
+        <v>-7525</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,26 +6131,26 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>11189</v>
+        <v>15525</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-7540</v>
+        <v>-3197</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
@@ -6176,26 +6176,26 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>15064</v>
+        <v>11155</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-3665</v>
+        <v>-7567</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
@@ -6221,30 +6221,30 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>16411</v>
+        <v>15525</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-2318</v>
+        <v>-3197</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6270,13 +6270,13 @@
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>30</v>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>30</v>
@@ -6360,13 +6360,13 @@
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>16490</v>
+        <v>16342</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-2239</v>
+        <v>-2380</v>
       </c>
       <c r="G131" s="2" t="n">
         <v>20</v>
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G132" s="2" t="n">
         <v>30</v>
@@ -6450,13 +6450,13 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>15064</v>
+        <v>15525</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-3665</v>
+        <v>-3197</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>46</v>
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>30</v>
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>11217</v>
+        <v>11197</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-7512</v>
+        <v>-7525</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>30</v>
@@ -6585,26 +6585,26 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>12246</v>
+        <v>12998</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-6483</v>
+        <v>-5724</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6626,26 +6626,26 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>9540</v>
+        <v>8857</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-9189</v>
+        <v>-9865</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
@@ -6671,26 +6671,26 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>11189</v>
+        <v>9982</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-7540</v>
+        <v>-8740</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,26 +6716,26 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>9008</v>
+        <v>11155</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-9721</v>
+        <v>-7567</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
@@ -6765,13 +6765,13 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>30</v>
@@ -6810,13 +6810,13 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G141" s="2" t="n">
         <v>30</v>
@@ -6855,13 +6855,13 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>9540</v>
+        <v>9982</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-9189</v>
+        <v>-8740</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>23</v>
@@ -6900,13 +6900,13 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>11189</v>
+        <v>11155</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>18729</v>
+        <v>18722</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-7540</v>
+        <v>-7567</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>30</v>
@@ -6945,13 +6945,13 @@
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>11217</v>
+        <v>11671</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>9737</v>
+        <v>9703</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>1480</v>
+        <v>1968</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>46</v>

--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K144"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9689</v>
+        <v>10460</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9703</v>
+        <v>9605</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-14</v>
+        <v>855</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10177</v>
+        <v>10819</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10708</v>
+        <v>8611</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-531</v>
+        <v>2208</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10177</v>
+        <v>8128</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10708</v>
+        <v>7120</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-531</v>
+        <v>1008</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10540</v>
+        <v>6844</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10708</v>
+        <v>7120</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-168</v>
+        <v>-276</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11434</v>
+        <v>7907</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11713</v>
+        <v>7120</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-279</v>
+        <v>787</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6687</v>
+        <v>6610</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7692</v>
+        <v>6624</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1005</v>
+        <v>-14</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6924</v>
+        <v>7907</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7692</v>
+        <v>6624</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-768</v>
+        <v>1283</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8488</v>
+        <v>6844</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7692</v>
+        <v>7120</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>796</v>
+        <v>-276</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6924</v>
+        <v>6539</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7692</v>
+        <v>9605</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-768</v>
+        <v>-3066</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8209</v>
+        <v>6844</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7692</v>
+        <v>9605</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>517</v>
+        <v>-2761</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6687</v>
+        <v>7728</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7692</v>
+        <v>9605</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1005</v>
+        <v>-1877</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6924</v>
+        <v>8100</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7692</v>
+        <v>11606</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-768</v>
+        <v>-3506</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6924</v>
+        <v>8114</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7692</v>
+        <v>11606</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-768</v>
+        <v>-3492</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6687</v>
+        <v>8114</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7204</v>
+        <v>11606</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-517</v>
+        <v>-3492</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6924</v>
+        <v>8114</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7204</v>
+        <v>11606</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-280</v>
+        <v>-3492</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8209</v>
+        <v>8128</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7204</v>
+        <v>11606</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1005</v>
+        <v>-3478</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6687</v>
+        <v>6610</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6701</v>
+        <v>9605</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-14</v>
+        <v>-2995</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7985</v>
+        <v>6844</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6701</v>
+        <v>9605</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1284</v>
+        <v>-2761</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7385</v>
+        <v>7907</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9703</v>
+        <v>9605</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2318</v>
+        <v>-1698</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7985</v>
+        <v>6610</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1718</v>
+        <v>-3988</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8209</v>
+        <v>6617</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1494</v>
+        <v>-3981</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8181</v>
+        <v>6844</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-3532</v>
+        <v>-3754</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8209</v>
+        <v>6844</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-3504</v>
+        <v>-3754</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>8209</v>
+        <v>6610</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11713</v>
+        <v>11606</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-3504</v>
+        <v>-4996</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7985</v>
+        <v>8114</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11713</v>
+        <v>11606</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-3728</v>
+        <v>-3492</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9033</v>
+        <v>8418</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11713</v>
+        <v>11606</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-2680</v>
+        <v>-3188</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7385</v>
+        <v>10446</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9703</v>
+        <v>12599</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-2318</v>
+        <v>-2153</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1770,26 +1770,26 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7804</v>
+        <v>10819</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>9703</v>
+        <v>12599</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1899</v>
+        <v>-1780</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8209</v>
+        <v>11026</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9703</v>
+        <v>12599</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-1494</v>
+        <v>-1573</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,13 +1860,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7385</v>
+        <v>8597</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-2318</v>
+        <v>-2001</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7985</v>
+        <v>8761</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1718</v>
+        <v>-1837</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8209</v>
+        <v>8956</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1494</v>
+        <v>-1642</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8181</v>
+        <v>9536</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>10708</v>
+        <v>10598</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-2527</v>
+        <v>-1062</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>8209</v>
+        <v>8597</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10708</v>
+        <v>10598</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-2499</v>
+        <v>-2001</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8209</v>
+        <v>8956</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>10708</v>
+        <v>10598</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-2499</v>
+        <v>-1642</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>8181</v>
+        <v>8956</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-3532</v>
+        <v>-1642</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>30</v>
@@ -2147,9 +2147,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8209</v>
+        <v>8956</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-3504</v>
+        <v>-1642</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>30</v>
@@ -2192,9 +2192,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8488</v>
+        <v>9825</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-3225</v>
+        <v>-773</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2237,9 +2237,9 @@
       <c r="I39" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>11197</v>
+        <v>8956</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>12704</v>
+        <v>9605</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1507</v>
+        <v>-649</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>30</v>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>11434</v>
+        <v>9315</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>12704</v>
+        <v>9605</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1270</v>
+        <v>-290</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>12816</v>
+        <v>9591</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>12704</v>
+        <v>9605</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>112</v>
+        <v>-14</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>8684</v>
+        <v>8956</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>10708</v>
+        <v>9605</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-2024</v>
+        <v>-649</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>30</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>8857</v>
+        <v>9315</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10708</v>
+        <v>9605</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1851</v>
+        <v>-290</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10177</v>
+        <v>9591</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10708</v>
+        <v>9605</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-531</v>
+        <v>-14</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10652</v>
+        <v>8838</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>10708</v>
+        <v>11606</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-56</v>
+        <v>-2768</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>8684</v>
+        <v>8956</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10708</v>
+        <v>11606</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-2024</v>
+        <v>-2650</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>30</v>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>8935</v>
+        <v>8956</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>10708</v>
+        <v>11606</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1773</v>
+        <v>-2650</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10177</v>
+        <v>9591</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10708</v>
+        <v>11606</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-531</v>
+        <v>-2015</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>30</v>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11127</v>
+        <v>8956</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9703</v>
+        <v>9605</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>1424</v>
+        <v>-649</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>9689</v>
+        <v>9825</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>9703</v>
+        <v>9605</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-14</v>
+        <v>220</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10289</v>
+        <v>8956</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>586</v>
+        <v>-1642</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,30 +2846,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>9689</v>
+        <v>9315</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-14</v>
+        <v>-1283</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,26 +2891,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>10289</v>
+        <v>9591</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>9703</v>
+        <v>10598</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>586</v>
+        <v>-1007</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>8927</v>
+        <v>8597</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-2786</v>
+        <v>-2001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,26 +2981,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>9689</v>
+        <v>8761</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-2024</v>
+        <v>-1837</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>10568</v>
+        <v>8956</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1145</v>
+        <v>-1642</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>30</v>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,30 +3071,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11434</v>
+        <v>9315</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>11713</v>
+        <v>10598</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-279</v>
+        <v>-1283</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>10289</v>
+        <v>8956</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>9703</v>
+        <v>11606</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>586</v>
+        <v>-2650</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>9689</v>
+        <v>8956</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10708</v>
+        <v>11606</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1019</v>
+        <v>-2650</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>30</v>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3210,13 +3210,13 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10177</v>
+        <v>8956</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>10708</v>
+        <v>9605</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-531</v>
+        <v>-649</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>30</v>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>8684</v>
+        <v>9315</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>10708</v>
+        <v>9605</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-2024</v>
+        <v>-290</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,26 +3296,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>8857</v>
+        <v>9315</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10708</v>
+        <v>7617</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-1851</v>
+        <v>1698</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,26 +3341,26 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>10177</v>
+        <v>9315</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10708</v>
+        <v>7617</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-531</v>
+        <v>1698</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10289</v>
+        <v>9315</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10708</v>
+        <v>7617</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-419</v>
+        <v>1698</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>46</v>
@@ -3407,9 +3407,9 @@
       <c r="I65" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,26 +3431,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10568</v>
+        <v>9536</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11713</v>
+        <v>7617</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-1145</v>
+        <v>1919</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10568</v>
+        <v>14021</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11713</v>
+        <v>14090</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-1145</v>
+        <v>-69</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,26 +3521,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>10289</v>
+        <v>12668</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>9703</v>
+        <v>14090</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>586</v>
+        <v>-1422</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9689</v>
+        <v>14021</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-9033</v>
+        <v>-69</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3587,9 +3587,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,30 +3611,30 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10177</v>
+        <v>16450</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-8545</v>
+        <v>2360</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10289</v>
+        <v>12668</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-8433</v>
+        <v>-1422</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9689</v>
+        <v>14021</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-9033</v>
+        <v>-69</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3722,9 +3722,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>10289</v>
+        <v>12668</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-8433</v>
+        <v>-1422</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>11155</v>
+        <v>12668</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-7567</v>
+        <v>-1422</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>30</v>
@@ -3812,9 +3812,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,30 +3836,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>8935</v>
+        <v>12668</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-9787</v>
+        <v>-1422</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>12649</v>
+        <v>12668</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-6073</v>
+        <v>-1422</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>30</v>
@@ -3902,9 +3902,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>12788</v>
+        <v>14021</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-5934</v>
+        <v>-69</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>30</v>
@@ -3947,9 +3947,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>12788</v>
+        <v>12668</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-5934</v>
+        <v>-1422</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>30</v>
@@ -3992,9 +3992,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>10289</v>
+        <v>14021</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-8433</v>
+        <v>-69</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>12788</v>
+        <v>12668</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>18722</v>
+        <v>15580</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-5934</v>
+        <v>-2912</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>30</v>
@@ -4082,9 +4082,9 @@
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,17 +4106,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>10540</v>
+        <v>14021</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>18722</v>
+        <v>15580</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-8182</v>
+        <v>-1559</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>30</v>
@@ -4127,9 +4127,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,30 +4151,30 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>10652</v>
+        <v>14021</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18722</v>
+        <v>15580</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-8070</v>
+        <v>-1559</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>12788</v>
+        <v>14021</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>18722</v>
+        <v>15580</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-5934</v>
+        <v>-1559</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>30</v>
@@ -4217,9 +4217,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,30 +4241,30 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>8857</v>
+        <v>12668</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-9865</v>
+        <v>-1422</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>11197</v>
+        <v>14021</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-7525</v>
+        <v>-69</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>30</v>
@@ -4307,9 +4307,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,30 +4331,30 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>12216</v>
+        <v>12530</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-6506</v>
+        <v>-1560</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>12788</v>
+        <v>12668</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-5934</v>
+        <v>-1422</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>30</v>
@@ -4397,9 +4397,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-120</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>12649</v>
+        <v>12668</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-6073</v>
+        <v>-1422</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>30</v>
@@ -4442,9 +4442,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>12788</v>
+        <v>14021</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-5934</v>
+        <v>-69</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>30</v>
@@ -4487,9 +4487,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>29-AUG-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>12788</v>
+        <v>12668</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>18722</v>
+        <v>14090</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-5934</v>
+        <v>-1422</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>30</v>
@@ -4532,9 +4532,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,30 +4556,30 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-599</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>14789</v>
+        <v>11026</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-3933</v>
+        <v>-7535</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12788</v>
+        <v>11095</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-1424</v>
+        <v>-7466</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>30</v>
@@ -4622,9 +4622,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,30 +4646,30 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>12788</v>
+        <v>14835</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-1424</v>
+        <v>-3726</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>14143</v>
+        <v>11026</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-69</v>
+        <v>-7535</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>30</v>
@@ -4712,9 +4712,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>12788</v>
+        <v>11095</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-1424</v>
+        <v>-7466</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>30</v>
@@ -4757,9 +4757,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,30 +4781,30 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>12788</v>
+        <v>14835</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-1424</v>
+        <v>-3726</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>12788</v>
+        <v>11026</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-1424</v>
+        <v>-7535</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>30</v>
@@ -4847,9 +4847,9 @@
       <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>14156</v>
+        <v>11026</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-56</v>
+        <v>-7535</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>30</v>
@@ -4892,9 +4892,9 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-SEP-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>12788</v>
+        <v>11095</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-1424</v>
+        <v>-7466</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>30</v>
@@ -4937,9 +4937,9 @@
       <c r="I99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>14143</v>
+        <v>11026</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-69</v>
+        <v>-7535</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>30</v>
@@ -4982,9 +4982,9 @@
       <c r="I100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,30 +5006,30 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>12788</v>
+        <v>14835</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-1424</v>
+        <v>-3726</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>12788</v>
+        <v>11026</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15720</v>
+        <v>18561</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-2932</v>
+        <v>-7535</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>30</v>
@@ -5072,9 +5072,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>14156</v>
+        <v>11095</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15720</v>
+        <v>18561</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-1564</v>
+        <v>-7466</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>30</v>
@@ -5117,9 +5117,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,30 +5141,30 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>14156</v>
+        <v>14835</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>15720</v>
+        <v>18561</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-1564</v>
+        <v>-3726</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>14143</v>
+        <v>11026</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>15720</v>
+        <v>18561</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-1577</v>
+        <v>-7535</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>30</v>
@@ -5207,9 +5207,9 @@
       <c r="I105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>14156</v>
+        <v>11095</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15720</v>
+        <v>18561</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-1564</v>
+        <v>-7466</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>30</v>
@@ -5252,9 +5252,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,30 +5276,30 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>14156</v>
+        <v>14835</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>15720</v>
+        <v>18561</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-1564</v>
+        <v>-3726</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,26 +5321,26 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>14156</v>
+        <v>16098</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15720</v>
+        <v>18561</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-1564</v>
+        <v>-2463</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>12788</v>
+        <v>11026</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-1424</v>
+        <v>-7535</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>30</v>
@@ -5387,9 +5387,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>14143</v>
+        <v>11026</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-69</v>
+        <v>-7535</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>30</v>
@@ -5432,9 +5432,9 @@
       <c r="I110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nesma Airlines NE-120</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>12788</v>
+        <v>11095</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-1424</v>
+        <v>-7466</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>30</v>
@@ -5477,9 +5477,9 @@
       <c r="I111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,26 +5501,26 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>12788</v>
+        <v>16176</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-1424</v>
+        <v>-2385</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H112" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>14156</v>
+        <v>11026</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-56</v>
+        <v>-7535</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>30</v>
@@ -5567,9 +5567,9 @@
       <c r="I113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>29-AUG-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,30 +5591,30 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>12788</v>
+        <v>14835</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-1424</v>
+        <v>-3726</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>11155</v>
+        <v>11026</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-7567</v>
+        <v>-7535</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>30</v>
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>11197</v>
+        <v>11095</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-7525</v>
+        <v>-7466</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>30</v>
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>15525</v>
+        <v>12323</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-3197</v>
+        <v>-6238</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>46</v>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,26 +5771,26 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>11155</v>
+        <v>8761</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-7567</v>
+        <v>-9800</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5820,13 +5820,13 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>15525</v>
+        <v>9674</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-3197</v>
+        <v>-8887</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>46</v>
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-307</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>11155</v>
+        <v>11026</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-7567</v>
+        <v>-7535</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>30</v>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-107</t>
+          <t>Nesma Airlines NE-122</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>11155</v>
+        <v>11095</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-7567</v>
+        <v>-7466</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>30</v>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,26 +5951,26 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>11155</v>
+        <v>8838</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-7567</v>
+        <v>-9723</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,26 +5996,26 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-307</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>15525</v>
+        <v>11026</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-3197</v>
+        <v>-7535</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>Nile Air NP-107</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>11155</v>
+        <v>11026</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-7567</v>
+        <v>-7535</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>30</v>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,26 +6086,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-122</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>11197</v>
+        <v>9384</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-7525</v>
+        <v>-9177</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,26 +6131,26 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Nile Air NP-207</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>15525</v>
+        <v>11026</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>18722</v>
+        <v>18561</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-3197</v>
+        <v>-7535</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,798 +6176,33 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-207</t>
+          <t>EgyptAir MS-811</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>11155</v>
+        <v>11054</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>18722</v>
+        <v>9605</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-7567</v>
+        <v>1449</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>15525</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>-3197</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J128" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-599</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>16342</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>-2380</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>12-SEP-26</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>12-SEP-26</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>15525</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>-3197</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J133" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-122</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>11197</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>-7525</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
-        <v>12998</v>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>-5724</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-599</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>8857</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>-9865</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J137" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="n">
-        <v>9982</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>-8740</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-307</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-107</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>9982</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>-8740</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J142" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-207</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>11155</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>-7567</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>SM-325</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-811</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>11671</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>9703</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>1968</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
